--- a/outputs/chain-update-20261028/oshi_oshi.xlsx
+++ b/outputs/chain-update-20261028/oshi_oshi.xlsx
@@ -185,16 +185,16 @@
     <t>contractor</t>
   </si>
   <si>
-    <t>f971a04a-e247-46b2-8780-bc2c94895d90</t>
-  </si>
-  <si>
-    <t>8c264356-3144-4600-a0dd-99e491db6035</t>
+    <t>976ccfd1-657c-4ccb-94e9-0359243a38da</t>
+  </si>
+  <si>
+    <t>50e0e250-91a2-4339-9c44-b4ccf7d0fbef</t>
   </si>
   <si>
     <t>oshi_oshi</t>
   </si>
   <si>
-    <t>["89cf1821-72b3-4c89-91dc-dda7acdc2f13","cf61fba7-00ad-4d66-b23a-f20511104b42","0821a825-0557-4b30-bd61-a657a755cdce","f8e394a4-d615-44e1-9ee5-d336cee69506","b282e2b0-fec5-4a21-9b10-da97a8a97b3c","f0f7e86c-8794-4f60-91b2-ae611061df89","ae7bf8ae-4c15-44e2-9253-ec5246f86911","fcfab07d-8db2-4c1a-85fc-8ffdd92e5928","a034dc64-5238-4f6d-ac72-e171735cebcd","f5b9b0f2-a675-4189-835c-77177ec23456","1ef12c57-6844-4377-9536-1c8832d9430a","c88f8c19-50d0-4f8f-bf05-4ec81294ad24","db68935b-099f-4748-8872-86df3c0cdc54","c69dceb1-4be0-4306-a4d6-cee141b1b67c","6114ed4a-0542-455f-a7ed-1f5a61b2a057","f66b1b6b-82c7-4ecf-89c7-694d49025855","271c19a0-eccc-4801-a1e3-45ed2d1f81f9","6242246f-f711-4c70-a8a1-f1b154b12de4","16cc9239-2691-4917-b952-d47f6582819f","08aadde9-c0a6-438e-a608-b7f230bf1427","500fce2c-0b40-4874-945f-b08548d24364","38398255-8c0d-429c-bcac-98b4a88d3016"]</t>
+    <t>["8f1de1fc-ca3e-431f-b192-ecc8b3aa9a4e","d5281340-3c89-42f2-a4d7-aa121276be23","a6838c26-ac88-42a7-a211-6bd8b6e206ae","9d0635af-1493-448e-b0eb-8a86b7ad3735","52a8980d-1a1e-456c-a275-6cb317877d90","15440426-6b7f-464b-8fd6-8b3f80b99079","5c23aa9a-e527-4622-bf7f-e572db615e43","27a509d0-f182-4dd4-8acf-7b48effae61e","f244b921-de75-4a1e-b31f-169a76de8f40","b2491206-3675-4c1c-9617-1cb820e6b314","fb8e38d0-08c2-4ad3-af53-f7fc3fbfe00c","ed92a3c5-e6c0-4423-91b1-e3160bc0211d","5079f7e3-189e-4437-95ad-f4bea63eb6f9","bcdf1a47-7ad5-41e3-98ec-337ed4d0b87b","0b2f1edd-39a4-4d9a-af6c-33a31cf92007","54910830-5af9-42c6-98b1-00eb850c4be1","1180b9ef-818e-4823-b126-acbd807403d1","2577ab30-16d3-4819-976b-290f73ad7d3c","3877c570-2b33-4723-b84a-1dfe819dbda6","e72c10f2-f866-4d46-ad03-f660bf6e0d76","664212d3-4b7f-436a-bb74-68085aed58dd","9b35739e-ff39-499c-81fc-a655c0017d92"]</t>
   </si>
   <si>
     <t>layout</t>
@@ -221,136 +221,136 @@
     <t>rowIds</t>
   </si>
   <si>
-    <t>89cf1821-72b3-4c89-91dc-dda7acdc2f13</t>
-  </si>
-  <si>
-    <t>["c0d5aee2-4c84-4ad3-9e2b-d7c0a9492955","2858f0be-e9d1-4d79-85c1-02d2fa01d511","bfb510ee-fd38-45a8-8407-63f83b2cbc9d","ea4ec611-5c31-443c-9cc8-3b29aa60fb4f","3f0127a7-21fa-4f65-a78a-3847c0f49d84","099ce812-b36f-4b53-9b46-cdf7d8c82752","a3f31d66-b815-4793-8db0-ee6176920241","bbcba1a1-129b-4ee6-bd25-69a95a000901","6183dc62-52e2-4662-a1c3-553ac0ed70a9"]</t>
-  </si>
-  <si>
-    <t>cf61fba7-00ad-4d66-b23a-f20511104b42</t>
-  </si>
-  <si>
-    <t>["e9363238-00e2-49ad-bf3f-177d43e5e746","c7a971e5-e154-4ab9-90b2-530cbf7c54a9","da3762b4-478a-409f-b339-27827d6958b9","a1a0e11e-6a7d-431e-971e-a354902b8ca0","ff54d41f-863c-44e7-9b18-e3c1cbf2cc1c","59e45f4c-c08a-40e0-bbe5-c77b8428dd71","2ebb6518-d976-4be1-8423-a37d18804655"]</t>
-  </si>
-  <si>
-    <t>0821a825-0557-4b30-bd61-a657a755cdce</t>
-  </si>
-  <si>
-    <t>["a7ab8dfb-2c0a-48e6-b44b-800dc91b9939","dc9c9809-c204-4606-aef7-f1008e49e341","b2b72ee2-2fa9-44e7-aa39-bdddf082e3d1","3eab265c-1275-4a44-b790-b0871954a411","5b7b34cf-77b1-4822-9692-f6d95534cdfa","14251e6b-b7ce-46c8-9c6d-99b9832db87e","965b5eb5-98fb-4085-8d32-65a5049adb55","cef29ff1-613f-48e0-855e-eb296e7f3302","6365b3a7-ca7e-4e37-98a1-41740bf255d6"]</t>
-  </si>
-  <si>
-    <t>f8e394a4-d615-44e1-9ee5-d336cee69506</t>
-  </si>
-  <si>
-    <t>["f671a80d-911c-4daa-844e-9e29b1aeecb2","31a2e879-e495-4e9f-b2c2-008bbc51cbc8","b50b1425-a17f-4b5f-8aa1-f83a5e229ef7","10049eb0-576d-4170-98b6-e29d345d22be","381fe78a-9e9e-4ec5-907a-e3e8d2a0bdf3","bb2b4f4a-ffdd-4f27-b815-4331e3d14601","4a8f7e26-7728-4ae6-a197-237bc84c8c9a","e68ab009-c348-4fc0-a50b-5bcd4c93f05b","103626c3-c22e-447b-98fb-3dfebb9cdaeb","de8577f3-fa9c-4b4c-9cf6-05f5bdbe8c71","f0e4e920-3b04-4c22-9d93-e86d05c4d6b0"]</t>
-  </si>
-  <si>
-    <t>b282e2b0-fec5-4a21-9b10-da97a8a97b3c</t>
-  </si>
-  <si>
-    <t>["d739b3bc-780a-4a72-ba86-0ab69d5555d8","279664b5-0c3b-4d71-94ff-831a0ad7f0f2"]</t>
-  </si>
-  <si>
-    <t>f0f7e86c-8794-4f60-91b2-ae611061df89</t>
-  </si>
-  <si>
-    <t>["0b2c232b-b1ec-4d04-9327-63c5c169d60b","e3b5eca2-2a63-4dd4-9acb-ae3c70e63581"]</t>
-  </si>
-  <si>
-    <t>ae7bf8ae-4c15-44e2-9253-ec5246f86911</t>
-  </si>
-  <si>
-    <t>["88b108a2-ba3a-44cb-b624-e7f2d477a59b","6af4c878-c16d-4cdc-b056-b9017d9ed215"]</t>
-  </si>
-  <si>
-    <t>fcfab07d-8db2-4c1a-85fc-8ffdd92e5928</t>
-  </si>
-  <si>
-    <t>["035dd93f-ff8c-4c4f-82e0-fb95305e9064","e90f467b-62ad-4dc5-8390-2824cd47051d","2a77b2b0-bd89-484c-aefa-7649237266a3","529a5c22-b175-444b-a0a1-a79b20edce82","762c2a92-e28a-48bc-b6d4-aa7890919569","f33b6302-5f9a-4646-afa0-50840c5212fb","814e0b35-7c45-4f2e-9d46-c65e831796f3","11915dd1-408c-46c9-8a03-20d139f5f017"]</t>
-  </si>
-  <si>
-    <t>a034dc64-5238-4f6d-ac72-e171735cebcd</t>
-  </si>
-  <si>
-    <t>["b018f255-7f74-4926-bd9d-03ca8de14c5f","90d00fb0-cde4-4ea7-96e7-6fb4866f2cbf","6931ce28-5fc3-4d9d-9a0a-6f3b1dcc9430","a6e52682-36e0-454b-96bd-ee2696af011f","bbacb34f-969a-4784-82e4-352b2d5757d0"]</t>
-  </si>
-  <si>
-    <t>f5b9b0f2-a675-4189-835c-77177ec23456</t>
-  </si>
-  <si>
-    <t>["65d9619e-f59f-4ffb-979d-4f212dc38e6e","57de838b-c1ff-4814-8a3e-fc2ecf82c909","5249fb67-2ebb-416a-85de-0aeb02b82fc1","7c779bf6-5dc8-491e-a313-8a6ae8be25bd","1a5045ec-62d9-4b53-bf57-e987bd4be60d"]</t>
-  </si>
-  <si>
-    <t>1ef12c57-6844-4377-9536-1c8832d9430a</t>
-  </si>
-  <si>
-    <t>["e6d6b168-577f-48a1-a785-79c9ce0a98c3","505199b7-23f9-46a5-bae6-2ec608970020","72e7ba87-dc88-46de-9b6c-263b6f8a03c2","c3cd28e5-5d01-4c10-8fa1-6eb41b02e3cb","dc27ed35-c9b3-444b-a671-043c55df5ff9","fb19eebb-f858-4a25-81c9-76315e81b53b","d9d2e282-ac14-48e1-977b-b51cf959cf46","7ca31fc3-ad79-4d9c-af85-8438db16427e","6f64ed20-35c0-4c0c-ae0e-6bfddc26600c","e4142fab-622c-4c97-8e40-155fc06a2ee6","c07c12c9-f785-4ac9-ba64-8c3dd32fd7a1","f6272e14-b96a-4269-8f83-fe57fa052f79","1d16f450-db46-4817-83ae-c4be601a2593","1c434242-36b3-40c9-9d75-9f3d2131bdd2"]</t>
-  </si>
-  <si>
-    <t>c88f8c19-50d0-4f8f-bf05-4ec81294ad24</t>
-  </si>
-  <si>
-    <t>["ede56674-a0e0-4594-b46c-35708807b906","a91a7af2-dc99-450d-b0f0-e514181f4b96","6ac9c51a-c10d-4be4-a589-8ecbdee65bc9","e2972e79-9c46-48b0-90cc-f830e3330095","94c849cd-cf94-40cb-a323-fc827fb7177d","9c0d69cf-954b-4d90-80d9-eef1f2aa6d8a","be913337-5e8d-4009-8a1b-7543b0addea3","6d89502a-e2d8-4d8f-8c15-91e7883b0455","98ed4f35-d46a-47fc-b06a-06e1cbf28e04","a02b0c22-f069-471d-aac4-106aec900ad0","7bc1bad8-a136-40ed-a037-d1a04cc009a2"]</t>
-  </si>
-  <si>
-    <t>db68935b-099f-4748-8872-86df3c0cdc54</t>
-  </si>
-  <si>
-    <t>["1ea82966-c69b-4c57-ab84-7be26dd80dd7","99cb4301-2cf4-4688-afe7-32f8d8fbde3d","fefbffb3-a85b-4be5-9251-ca172d4de6bf","c4175152-e8a6-406f-8bda-4c454e4f5583"]</t>
-  </si>
-  <si>
-    <t>c69dceb1-4be0-4306-a4d6-cee141b1b67c</t>
-  </si>
-  <si>
-    <t>["0211a3d5-ce4e-46cb-82c0-2b1d9cfa8562","4e57bc45-072e-4150-b60e-fd86cf1d2ef8","83e364dc-1b36-4b81-a311-5d68d8e524f2","11c7765a-0e84-4cbf-89f1-f330a0932a0f"]</t>
-  </si>
-  <si>
-    <t>6114ed4a-0542-455f-a7ed-1f5a61b2a057</t>
-  </si>
-  <si>
-    <t>["05e0039a-1dac-4677-95a7-679d514b9228","d79791c7-a25c-413d-af24-d032985ea078","41ea2e75-51bf-4b18-86a4-c3a2d83568a1","f7ba6162-7a3c-409e-9652-9d29de9cd080"]</t>
-  </si>
-  <si>
-    <t>f66b1b6b-82c7-4ecf-89c7-694d49025855</t>
-  </si>
-  <si>
-    <t>["a6b1da0d-28be-4b30-939d-973a7d8c8ccf","4430e329-d945-41f7-a764-feb500d143c7"]</t>
-  </si>
-  <si>
-    <t>271c19a0-eccc-4801-a1e3-45ed2d1f81f9</t>
-  </si>
-  <si>
-    <t>["bebd7028-32ab-4e90-9cae-d17a27cbacdc","bd805dde-5240-4b77-ad6f-adb0d8432d13"]</t>
-  </si>
-  <si>
-    <t>6242246f-f711-4c70-a8a1-f1b154b12de4</t>
-  </si>
-  <si>
-    <t>["cf1f2c8b-f851-4583-bee3-355c9d5508ff","f37a71cd-2251-46bf-a7f4-f9a14e3dbe6f"]</t>
-  </si>
-  <si>
-    <t>16cc9239-2691-4917-b952-d47f6582819f</t>
-  </si>
-  <si>
-    <t>["080669c8-5251-411c-a0cf-4d05eaf25115","3d054596-1420-40d4-a88b-ed47366d45f6","107122bc-7559-4a35-aa88-0f04c5ac4ced"]</t>
-  </si>
-  <si>
-    <t>08aadde9-c0a6-438e-a608-b7f230bf1427</t>
-  </si>
-  <si>
-    <t>["48aa3c72-d099-44cc-94af-690fe47fbbf6","bff4b214-9be8-46d8-849c-8aea60c0700f"]</t>
-  </si>
-  <si>
-    <t>500fce2c-0b40-4874-945f-b08548d24364</t>
-  </si>
-  <si>
-    <t>["7427a35d-c54b-4cac-8b50-59f437a2794d","91ab0439-3352-4b64-a5ca-14e972a80379"]</t>
-  </si>
-  <si>
-    <t>38398255-8c0d-429c-bcac-98b4a88d3016</t>
-  </si>
-  <si>
-    <t>["88841134-2c8c-417b-8acc-6af740ad63ab","7e283deb-a816-4e49-8ff9-9746925aaea4","ac68329b-2b1b-4798-a718-ec48d7b8138e"]</t>
+    <t>8f1de1fc-ca3e-431f-b192-ecc8b3aa9a4e</t>
+  </si>
+  <si>
+    <t>["87d41435-68ad-45d5-bea6-77151c8a2298","c8d35d68-efe3-4a2c-9eef-7f835c9f5b67","c2ed9080-9e23-4de6-9628-af9bf7675fb2","f46d3702-1fa9-471d-ade0-d502f81117f6","bc8a4109-26b0-4bf5-8038-0f7aaa25e615","1a75bbb8-2f72-46c0-86b1-308b2594f1c9","e0c94c02-6bf2-4b1e-96bb-a1c54bd74cd4","cdf5f892-52e9-4933-8726-770e49a3997d","f16cad0b-1583-48ff-bc4a-07d3a6225a20"]</t>
+  </si>
+  <si>
+    <t>d5281340-3c89-42f2-a4d7-aa121276be23</t>
+  </si>
+  <si>
+    <t>["6c4877c6-d9e9-4e82-8fdc-626e8b3bf4e8","c6c02053-142e-4fac-8e6d-1d8a27cd9113","1f91343a-40ff-4d8d-8a6a-6f9806b64000","1ad1f1bb-0606-4bfe-ac0c-c50f8f032a03","ff698eb3-99f7-47f2-9561-f32f50b55734","c15c465d-e70e-4fa5-b4de-ce2d5d36a520","38f3deaf-e597-4048-afe1-677aa4c8445e"]</t>
+  </si>
+  <si>
+    <t>a6838c26-ac88-42a7-a211-6bd8b6e206ae</t>
+  </si>
+  <si>
+    <t>["773751de-3b5b-4d90-a66b-71721ca62b2f","9ef27652-0a46-42b4-98e6-a7ac063c4fd7","675568d2-83a5-44e3-989b-c6f222e5a9a2","cb02decc-33a5-4472-81ed-2642005d6a31","de35b9ea-113d-447c-bab8-9f2391502f9c","7e355058-3a14-434a-94fb-752bd905ea81","a1791ccd-7ca2-48c0-81f0-e96619aa9638","ab2e53b6-4fb4-4eb2-844c-259e51377d37","8a05c96b-09a9-4c49-9725-ff4da2072f4a"]</t>
+  </si>
+  <si>
+    <t>9d0635af-1493-448e-b0eb-8a86b7ad3735</t>
+  </si>
+  <si>
+    <t>["2e853e8d-fbc1-449e-9b52-66425cfe045e","e383cafa-ad72-4355-975d-b023d822f919","0b3b29b5-02cc-43d4-a9de-e3e973b06f45","17326ac6-7cdd-4810-8a40-cdd2a305bc6d","b0e7815b-41d6-4a1f-9825-9c55248e08d3","bd93f2b8-2293-4fa3-a966-cf21beae8c51","83ea5318-aa20-4f55-a653-b2cf96d92f3b","13d96bd7-dc13-410b-b6cb-646ae608dfa5","51dc9642-f988-4f17-af7b-735b442ebee7","5520b05d-bdfa-4332-a12f-24a9897b74ae","fc265f73-e95a-4234-bf48-3d6f91649c2a"]</t>
+  </si>
+  <si>
+    <t>52a8980d-1a1e-456c-a275-6cb317877d90</t>
+  </si>
+  <si>
+    <t>["466a0621-8084-4e13-824b-06ae1f293800","2b141977-e021-40a8-8fd8-2bb1acf7ca3f"]</t>
+  </si>
+  <si>
+    <t>15440426-6b7f-464b-8fd6-8b3f80b99079</t>
+  </si>
+  <si>
+    <t>["f3209273-36ce-4d6a-ac79-bc18b5548b72","0f75327e-0b16-4fe7-8d77-a9961ba5cc1d"]</t>
+  </si>
+  <si>
+    <t>5c23aa9a-e527-4622-bf7f-e572db615e43</t>
+  </si>
+  <si>
+    <t>["63ac9297-c59f-448c-9459-dd385c66d45d","e1d1d7bc-add2-4884-a3fb-2ba4ca89882f"]</t>
+  </si>
+  <si>
+    <t>27a509d0-f182-4dd4-8acf-7b48effae61e</t>
+  </si>
+  <si>
+    <t>["35e5aa32-724f-47f4-92d6-cd9c196ae039","1838623b-1265-4771-8b4f-14c4918d71a9","570f8e88-c1cf-4c28-91f2-76723bc2a3e6","900d0ac8-48b8-4a8c-8e02-62dd1d546a3a","6e097459-54cc-492d-bc9c-d0c8168bf850","dd5201ff-eb88-461a-8da5-e717ed909599","d67482ad-99ef-4b70-8543-9de3903af4d8","0b47133c-479e-4989-9009-be435e0a1e7a"]</t>
+  </si>
+  <si>
+    <t>f244b921-de75-4a1e-b31f-169a76de8f40</t>
+  </si>
+  <si>
+    <t>["5fe46611-2156-4845-a8ca-6de5a2968eac","94a2f4c0-8a6c-40c7-8e0b-bd22f2c82024","b92e9bbf-dbb1-4932-b6eb-ba05c41d1a6d","2548a76c-218d-4735-9c82-8595246435a4","200d153c-3880-422c-be48-186932574514"]</t>
+  </si>
+  <si>
+    <t>b2491206-3675-4c1c-9617-1cb820e6b314</t>
+  </si>
+  <si>
+    <t>["ff4fda8e-44ca-4e66-aea4-8586cf037eee","aa7c38e3-7c39-4609-b349-3201da5ef546","11ede202-65ea-42e0-ae43-ec839b1b841b","a62c4017-3217-41f3-8aad-89716a35cb01","b3854162-78a5-4760-9ff7-64b9eca3316c"]</t>
+  </si>
+  <si>
+    <t>fb8e38d0-08c2-4ad3-af53-f7fc3fbfe00c</t>
+  </si>
+  <si>
+    <t>["c7c452c8-034b-4325-ad1e-b6c72cd84fd5","314a0c16-a1bb-446f-bbdd-3516edb578da","1284b05b-d161-4cbd-9bd4-517f508ac88a","a2a5f016-b272-4556-804c-9a598da427b3","3d946359-6da5-478a-badd-081bc2ba3fb3","80cd262b-465a-4ccd-9cda-c7285cfef908","2ddb3181-1b11-471e-9105-3351f2332baa","dafbd9d0-14a8-4c28-bcf1-c3c71c56d838","2cbaad5d-fa81-4afe-875b-c926b41bfc2d","9697302d-8585-44b5-8562-dd6046e1a8e6","cde0afea-e4ef-4775-9bdf-bc12b3754800","f1d2acc2-0836-4bf8-8fae-ebb2d4a18571","a51d5e6d-6622-40ae-9c64-47e2ff9dd120","0b0a7863-bedc-4c8d-bad6-a8dedfe73fec"]</t>
+  </si>
+  <si>
+    <t>ed92a3c5-e6c0-4423-91b1-e3160bc0211d</t>
+  </si>
+  <si>
+    <t>["fa095c4a-4c90-4463-bfb4-682e0ca9062b","b0494e87-dac8-43bc-a9b5-90bd179dbc6e","eaa91bda-8631-41e4-ade6-045109456fa7","c8bd28b8-ef06-41c4-b18d-dd6a6504429c","330a2b4f-4ccf-4ed0-88e6-20c23dfeca96","c92f7217-8246-47b5-9497-9db6a7420a18","086f6518-8b58-4b13-9450-e1f942c8b2a9","4f1f2684-8a1d-48b8-ac20-8e8db4dbb59a","f31152df-c05a-4c0e-89a9-4aa9748cda46","222656ae-b086-4f27-a513-39f7961e14cf","dd8305f9-3647-4580-a410-6624bb3a9066"]</t>
+  </si>
+  <si>
+    <t>5079f7e3-189e-4437-95ad-f4bea63eb6f9</t>
+  </si>
+  <si>
+    <t>["1ef068b8-bfee-4478-9d47-4b705e3a1eed","3bf875f0-b047-4a1c-b2aa-2997cce118ac","2d3467f9-77ec-489a-a2d9-137eb72cdeb8","80b61e81-d496-453b-a802-d9da6490201b"]</t>
+  </si>
+  <si>
+    <t>bcdf1a47-7ad5-41e3-98ec-337ed4d0b87b</t>
+  </si>
+  <si>
+    <t>["aa64a5c3-1fde-4a02-855d-db6bcc40b63a","4da5fed6-9025-45f6-8b18-262526c07257","0f377f48-8b6a-41a2-b9ea-1ba1333d5643","2023545f-de8c-4a30-ac50-27d62cddb5de"]</t>
+  </si>
+  <si>
+    <t>0b2f1edd-39a4-4d9a-af6c-33a31cf92007</t>
+  </si>
+  <si>
+    <t>["42b64bf1-81a5-4fc1-b144-3cddd79145c2","55fa57c7-5102-40fd-90da-42b9f2068bb2","2ea98e58-f874-4df7-833e-40ed1151d327","a2f5b446-8f69-4c32-a95f-d74ed018a127"]</t>
+  </si>
+  <si>
+    <t>54910830-5af9-42c6-98b1-00eb850c4be1</t>
+  </si>
+  <si>
+    <t>["03e87163-14de-4ff4-9b63-6183c8882f4b","cc25561a-8006-4171-80c2-b2d42d5f15b7"]</t>
+  </si>
+  <si>
+    <t>1180b9ef-818e-4823-b126-acbd807403d1</t>
+  </si>
+  <si>
+    <t>["b49ae10f-91d0-4711-9d26-53ec6031d7ff","29fac985-8557-4545-aeea-e98df925979f"]</t>
+  </si>
+  <si>
+    <t>2577ab30-16d3-4819-976b-290f73ad7d3c</t>
+  </si>
+  <si>
+    <t>["f4677fe2-94a7-4b2c-8a28-ac354fff9754","136d92f1-3993-4801-becf-ca6acb7f956a"]</t>
+  </si>
+  <si>
+    <t>3877c570-2b33-4723-b84a-1dfe819dbda6</t>
+  </si>
+  <si>
+    <t>["bd3a46f2-c266-4b6a-85fe-a61e73609c47","5336b120-3c66-4cb9-bbd6-5be324f9a39c","12a85cbe-935c-4c27-b2e3-20141cbdff48"]</t>
+  </si>
+  <si>
+    <t>e72c10f2-f866-4d46-ad03-f660bf6e0d76</t>
+  </si>
+  <si>
+    <t>["3e79e6a9-c603-42b5-888a-b35ece603bf0","56baad86-dc2b-4109-8635-d03819f35de7"]</t>
+  </si>
+  <si>
+    <t>664212d3-4b7f-436a-bb74-68085aed58dd</t>
+  </si>
+  <si>
+    <t>["e2e66179-3668-4d9d-9f89-e126fe016753","ea5e50ce-89d0-4beb-9cf1-c103877e25c6"]</t>
+  </si>
+  <si>
+    <t>9b35739e-ff39-499c-81fc-a655c0017d92</t>
+  </si>
+  <si>
+    <t>["fd7777c9-30f0-4ed3-a58c-3afb7aa6c74e","eb27c2bf-90cf-48a8-82dd-80c2554e74a5","522865dc-2d1d-4631-af4e-664495d739e8"]</t>
   </si>
   <si>
     <t>chapter</t>
@@ -380,7 +380,7 @@
     <t>מחירי עבודות הפירוק כוללים הגנה על הרכוש הנותר ופינוי הפסולת הנוצרת מהפירוק. פריטים המיועדים לשימוש חוזר יזוהו בפרויקט ויפורקו לשמירה. אין לחייב שוב אותו פינוי בסעיף אחר.</t>
   </si>
   <si>
-    <t>c0d5aee2-4c84-4ad3-9e2b-d7c0a9492955</t>
+    <t>87d41435-68ad-45d5-bea6-77151c8a2298</t>
   </si>
   <si>
     <t>note</t>
@@ -395,7 +395,7 @@
     <t>מ"ר</t>
   </si>
   <si>
-    <t>2858f0be-e9d1-4d79-85c1-02d2fa01d511</t>
+    <t>c8d35d68-efe3-4a2c-9eef-7f835c9f5b67</t>
   </si>
   <si>
     <t>item</t>
@@ -407,7 +407,7 @@
     <t>פירוק תקרה או הנמכה מסוג {סוג} באזור {אזור}, לרבות התשתית המיועדת לפירוק. הטיפול בחלקים: {פינוי או שמירה להרכבה מחדש}.</t>
   </si>
   <si>
-    <t>bfb510ee-fd38-45a8-8407-63f83b2cbc9d</t>
+    <t>c2ed9080-9e23-4de6-9628-af9bf7675fb2</t>
   </si>
   <si>
     <t>1.03</t>
@@ -416,7 +416,7 @@
     <t>פירוק ריצוף ושכבות תשתית באזור {אזור}, עד {גבול ועומק פירוק}, כהכנה לעבודות החדשות המפורטות בפרויקט.</t>
   </si>
   <si>
-    <t>ea4ec611-5c31-443c-9cc8-3b29aa60fb4f</t>
+    <t>f46d3702-1fa9-471d-ade0-d502f81117f6</t>
   </si>
   <si>
     <t>1.04</t>
@@ -428,7 +428,7 @@
     <t>קומפ'</t>
   </si>
   <si>
-    <t>3f0127a7-21fa-4f65-a78a-3847c0f49d84</t>
+    <t>bc8a4109-26b0-4bf5-8038-0f7aaa25e615</t>
   </si>
   <si>
     <t>1.05</t>
@@ -437,7 +437,7 @@
     <t>פירוק מערכת חשמל ואביזריה באזור {אזור}, בגבולות הנקובים בתכנון. מעגלים ואביזרים שנשארים פעילים או מיועדים להרכבה מחדש: {פירוט}.</t>
   </si>
   <si>
-    <t>099ce812-b36f-4b53-9b46-cdf7d8c82752</t>
+    <t>1a75bbb8-2f72-46c0-86b1-308b2594f1c9</t>
   </si>
   <si>
     <t>1.06</t>
@@ -446,7 +446,7 @@
     <t>פירוק צנרת ואביזרי אינסטלציה המיועדים להחלפה באזור {אזור}, בגבולות {תחילה וסיום}; הגנת וחסימת קצוות החיבור לפי התכנון.</t>
   </si>
   <si>
-    <t>a3f31d66-b815-4793-8db0-ee6176920241</t>
+    <t>e0c94c02-6bf2-4b1e-96bb-a1c54bd74cd4</t>
   </si>
   <si>
     <t>1.07</t>
@@ -458,7 +458,7 @@
     <t>יח'</t>
   </si>
   <si>
-    <t>bbcba1a1-129b-4ee6-bd25-69a95a000901</t>
+    <t>cdf5f892-52e9-4933-8726-770e49a3997d</t>
   </si>
   <si>
     <t>1.08</t>
@@ -467,7 +467,7 @@
     <t>פירוק שילוט קיים מטיפוס {זיהוי}, כולל רכיבי התקנה והזנה המיועדים לפירוק, ושמירה על רכיבים שסומנו להמשך שימוש.</t>
   </si>
   <si>
-    <t>6183dc62-52e2-4662-a1c3-553ac0ed70a9</t>
+    <t>f16cad0b-1583-48ff-bc4a-07d3a6225a20</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 1 להעברה</t>
@@ -479,7 +479,7 @@
     <t>מחירי המחיצות כוללים את רכיבי המערכת, התשתית, החיבורים והגמר המוגדרים בסעיף. סוגי לוחות, שכבות, בידוד ועיגון יושלמו לפי הפרויקט. גמר צבע וחיפוי מתומחרים בפרקים המיועדים להם, אלא אם הוגדר אחרת במפורש.</t>
   </si>
   <si>
-    <t>e9363238-00e2-49ad-bf3f-177d43e5e746</t>
+    <t>6c4877c6-d9e9-4e82-8fdc-626e8b3bf4e8</t>
   </si>
   <si>
     <t>2.01</t>
@@ -489,7 +489,7 @@
 גובה: {גובה}; עובי ומבנה המערכת: {מפרט}; לוחות: {סוג ושכבות}; בידוד: {מפרט}; בסיס ועיגון: {פרט}.</t>
   </si>
   <si>
-    <t>c7a971e5-e154-4ab9-90b2-530cbf7c54a9</t>
+    <t>c6c02053-142e-4fac-8e6d-1d8a27cd9113</t>
   </si>
   <si>
     <t>2.02</t>
@@ -498,7 +498,7 @@
     <t>ביצוע עיבוי או חיפוי קיר קיים במערכת {סוג}, בגובה {גובה}, באזור {אזור}, לצורך {ייעוד}, לרבות תשתית וחיבורים כמפורט.</t>
   </si>
   <si>
-    <t>da3762b4-478a-409f-b339-27827d6958b9</t>
+    <t>1f91343a-40ff-4d8d-8a6a-6f9806b64000</t>
   </si>
   <si>
     <t>2.03</t>
@@ -510,7 +510,7 @@
     <t>מ.א.</t>
   </si>
   <si>
-    <t>a1a0e11e-6a7d-431e-971e-a354902b8ca0</t>
+    <t>1ad1f1bb-0606-4bfe-ac0c-c50f8f032a03</t>
   </si>
   <si>
     <t>2.04</t>
@@ -519,7 +519,7 @@
     <t>אספקה והתקנת מגן פינה מנירוסטה מטיפוס {טיפוס}, במידות {מידות}, עובי וגמר {מפרט}, על תשתית {סוג} ובאופן חיבור {פרט}.</t>
   </si>
   <si>
-    <t>ff54d41f-863c-44e7-9b18-e3c1cbf2cc1c</t>
+    <t>ff698eb3-99f7-47f2-9561-f32f50b55734</t>
   </si>
   <si>
     <t>2.05</t>
@@ -528,7 +528,7 @@
     <t>אספקה והתקנת מגן קצה מנירוסטה מטיפוס {טיפוס}, במידות {מידות}, עובי וגמר {מפרט}, על תשתית {סוג} ובאופן חיבור {פרט}.</t>
   </si>
   <si>
-    <t>59e45f4c-c08a-40e0-bbe5-c77b8428dd71</t>
+    <t>c15c465d-e70e-4fa5-b4de-ce2d5d36a520</t>
   </si>
   <si>
     <t>2.06</t>
@@ -537,7 +537,7 @@
     <t>אספקה והתקנת משקוף נירוסטה לפתח {זיהוי וייעוד}, במידות {מידות}, עובי וגמר {מפרט}, לרבות החיבורים והעיגון שנקבעו לפריט.</t>
   </si>
   <si>
-    <t>2ebb6518-d976-4be1-8423-a37d18804655</t>
+    <t>38f3deaf-e597-4048-afe1-677aa4c8445e</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 2 להעברה</t>
@@ -546,7 +546,7 @@
     <t>מערכת המים והדלוחין תבוצע לפי תכנון הפרויקט. המחירים כוללים צנרת ואביזרי תשתית, חיבורים, הכנות ובדיקות כפי שנקבעו במפרט. אספקת כלים סניטריים וציוד אינה כלולה בסעיפי התקנה בלבד. קיום מערכת באתר אינו מעיד שאינה דורשת התאמה.</t>
   </si>
   <si>
-    <t>a7ab8dfb-2c0a-48e6-b44b-800dc91b9939</t>
+    <t>773751de-3b5b-4d90-a66b-71721ca62b2f</t>
   </si>
   <si>
     <t>3.01</t>
@@ -555,7 +555,7 @@
     <t>ביצוע או התאמת מערכת מים ודלוחין באזור {אזור}, בין נקודות החיבור {תחילה וסיום}, לרבות {צנרת, אביזרים ומתקנים}, לפי תכנון {הפניה}. חיבור למערכת קיימת יוגדר לפי מצב האתר שנבדק.</t>
   </si>
   <si>
-    <t>dc9c9809-c204-4606-aef7-f1008e49e341</t>
+    <t>9ef27652-0a46-42b4-98e6-a7ac063c4fd7</t>
   </si>
   <si>
     <t>3.02</t>
@@ -567,7 +567,7 @@
     <t>נק'</t>
   </si>
   <si>
-    <t>b2b72ee2-2fa9-44e7-aa39-bdddf082e3d1</t>
+    <t>675568d2-83a5-44e3-989b-c6f222e5a9a2</t>
   </si>
   <si>
     <t>3.03</t>
@@ -576,7 +576,7 @@
     <t>ביצוע נקודת מים קרים ודלוחין עבור {כיור או ציוד}, לפי תכנון הפרויקט, לרבות הצנרת ואביזרי החיבור בגבולות {תכולה}.</t>
   </si>
   <si>
-    <t>3eab265c-1275-4a44-b790-b0871954a411</t>
+    <t>cb02decc-33a5-4472-81ed-2642005d6a31</t>
   </si>
   <si>
     <t>3.04</t>
@@ -585,7 +585,7 @@
     <t>ביצוע נקודת דלוחין עצמאית עבור {ציוד או ייעוד}, לרבות חיבור וסיום לפי תכנון הפרויקט. אין לכלול שוב ניקוז שכבר נכלל בנקודת מים משולבת.</t>
   </si>
   <si>
-    <t>5b7b34cf-77b1-4822-9692-f6d95534cdfa</t>
+    <t>de35b9ea-113d-447c-bab8-9f2391502f9c</t>
   </si>
   <si>
     <t>3.05</t>
@@ -594,7 +594,7 @@
     <t>ביצוע נקודת ניקוז למיזוג אוויר מטיפוס {טיפוס}, לפי תכנון המיזוג והתברואה; קצה וגבול החיבור לקבלן המיזוג: {פירוט}.</t>
   </si>
   <si>
-    <t>14251e6b-b7ce-46c8-9c6d-99b9832db87e</t>
+    <t>7e355058-3a14-434a-94fb-752bd905ea81</t>
   </si>
   <si>
     <t>3.06</t>
@@ -603,7 +603,7 @@
     <t>התקנת תעלת ניקוז מטיפוס {טיפוס}, במידות {מידות}, על התשתית המוגדרת, וחיבורה למערכת הניקוז. אספקת התעלה, עיגון ואיטום המפגש: {חלוקת אחריות}.</t>
   </si>
   <si>
-    <t>965b5eb5-98fb-4085-8d32-65a5049adb55</t>
+    <t>a1791ccd-7ca2-48c0-81f0-e96619aa9638</t>
   </si>
   <si>
     <t>3.07</t>
@@ -612,7 +612,7 @@
     <t>התקנת מכל הדחה סמוי וכלי סניטרי מטיפוס {טיפוס} על תשתית {בלוק או מערכת אחרת}, לרבות חיבורים ותכולת ההתקנה שנקבעה. אספקת הכלי והמכל: {אחריות}.</t>
   </si>
   <si>
-    <t>cef29ff1-613f-48e0-855e-eb296e7f3302</t>
+    <t>ab2e53b6-4fb4-4eb2-844c-259e51377d37</t>
   </si>
   <si>
     <t>3.08</t>
@@ -621,7 +621,7 @@
     <t>אספקה והתקנת מתקן חימום מים מסוג {סוג}, בקיבול או הספק {נתון}, עם אביזרים וחיבורים כמפורט בתכנון. גבולות עבודות החשמל ועיגון המתקן: {פירוט}.</t>
   </si>
   <si>
-    <t>6365b3a7-ca7e-4e37-98a1-41740bf255d6</t>
+    <t>8a05c96b-09a9-4c49-9725-ff4da2072f4a</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 3 להעברה</t>
@@ -630,7 +630,7 @@
     <t>עבודות החשמל כוללות תשתית, מוליכים, חיבורים ואביזרים רק בתכולה המוגדרת לכל סעיף ולפי תכנון החשמל. הכנת נקודה, התקנת גוף ואספקת גוף הן תכולות שונות. חתכי מוליכים, קטרים, הגנות, הספקים ואופן הבדיקה ייקבעו בתכנון ולא יועתקו מפרויקט קודם.</t>
   </si>
   <si>
-    <t>f671a80d-911c-4daa-844e-9e29b1aeecb2</t>
+    <t>2e853e8d-fbc1-449e-9b52-66425cfe045e</t>
   </si>
   <si>
     <t>4.01</t>
@@ -639,7 +639,7 @@
     <t>ביצוע נקודת הפעלה וחיבור למעגל תאורה מטיפוס {טיפוס}, באזור {אזור}, לפי תכנון החשמל, כולל {תשתית, חיבור ואביזרי הפעלה}. אספקת והתקנת גופי התאורה אינן נכללות בסעיף זה.</t>
   </si>
   <si>
-    <t>31a2e879-e495-4e9f-b2c2-008bbc51cbc8</t>
+    <t>e383cafa-ad72-4355-975d-b023d822f919</t>
   </si>
   <si>
     <t>4.02</t>
@@ -648,7 +648,7 @@
     <t>ביצוע יציאה נוספת לגוף תאורה המשויך למעגל {זיהוי}, לפי תכנון החשמל; תכולת החיבור: {פירוט}.</t>
   </si>
   <si>
-    <t>b50b1425-a17f-4b5f-8aa1-f83a5e229ef7</t>
+    <t>0b3b29b5-02cc-43d4-a9de-e3e973b06f45</t>
   </si>
   <si>
     <t>4.03</t>
@@ -657,7 +657,7 @@
     <t>התקנת וחיבור גוף תאורה מטיפוס {טיפוס} על תשתית {קיימת או חדשה}, לרבות אביזרי ההתקנה המוגדרים. אספקת הגוף: {אחריות}.</t>
   </si>
   <si>
-    <t>10049eb0-576d-4170-98b6-e29d345d22be</t>
+    <t>17326ac6-7cdd-4810-8a40-cdd2a305bc6d</t>
   </si>
   <si>
     <t>4.04</t>
@@ -666,7 +666,7 @@
     <t>ביצוע נקודת כוח חד־פאזית עבור {ייעוד}, באזור {אזור}, עם האביזר והתשתית לפי תכנון החשמל ובגבולות {תכולה}.</t>
   </si>
   <si>
-    <t>381fe78a-9e9e-4ec5-907a-e3e8d2a0bdf3</t>
+    <t>b0e7815b-41d6-4a1f-9825-9c55248e08d3</t>
   </si>
   <si>
     <t>4.05</t>
@@ -675,7 +675,7 @@
     <t>ביצוע נקודת כוח תלת־פאזית עבור {ציוד}, לפי מפרט ההזנה של מתכנן החשמל ויצרן הציוד. אביזר החיבור וגבול העבודה: {פירוט}.</t>
   </si>
   <si>
-    <t>bb2b4f4a-ffdd-4f27-b815-4331e3d14601</t>
+    <t>bd93f2b8-2293-4fa3-a966-cf21beae8c51</t>
   </si>
   <si>
     <t>4.06</t>
@@ -684,7 +684,7 @@
     <t>ביצוע נקודת הזנה למיזוג אוויר עבור {יחידה}, בהתאם לתכנון החשמל והמיזוג, לרבות אביזר סיום וגבול חיבור {פירוט}.</t>
   </si>
   <si>
-    <t>4a8f7e26-7728-4ae6-a197-237bc84c8c9a</t>
+    <t>83ea5318-aa20-4f55-a653-b2cf96d92f3b</t>
   </si>
   <si>
     <t>4.07</t>
@@ -693,7 +693,7 @@
     <t>ביצוע נקודת הזנה למפוח עבור {יחידה וייעוד}, בהתאם לתכנון החשמל והאוורור, לרבות אביזר סיום וגבול חיבור {פירוט}.</t>
   </si>
   <si>
-    <t>e68ab009-c348-4fc0-a50b-5bcd4c93f05b</t>
+    <t>13d96bd7-dc13-410b-b6cb-646ae608dfa5</t>
   </si>
   <si>
     <t>4.08</t>
@@ -702,7 +702,7 @@
     <t>ביצוע תשתית תקשורת מטיפוס {סוג}, בין נקודות {קצוות}, לרבות צנרת, חוט משיכה ואביזרי סיום שנקבעו. כבילה פעילה וציוד קצה: {תכולה ואחריות}.</t>
   </si>
   <si>
-    <t>103626c3-c22e-447b-98fb-3dfebb9cdaeb</t>
+    <t>51dc9642-f988-4f17-af7b-735b442ebee7</t>
   </si>
   <si>
     <t>4.09</t>
@@ -711,7 +711,7 @@
     <t>אספקה והתקנת לוח חשמל {זיהוי}, כולל מכלול הרכיבים, הסימון, החיווט והחיבור שנקבעו בתכנון החשמל. גודל החיבור והמפרט יושלמו בפרויקט.</t>
   </si>
   <si>
-    <t>de8577f3-fa9c-4b4c-9cf6-05f5bdbe8c71</t>
+    <t>5520b05d-bdfa-4332-a12f-24a9897b74ae</t>
   </si>
   <si>
     <t>4.10</t>
@@ -720,7 +720,7 @@
     <t>ביצוע מערכת תאורת חירום בתכולת {היקף}, לפי תכנון החשמל והבטיחות המאושרים לפרויקט; אספקה, התקנה וחיבורים: {פירוט}.</t>
   </si>
   <si>
-    <t>f0e4e920-3b04-4c22-9d93-e86d05c4d6b0</t>
+    <t>fc265f73-e95a-4234-bf48-3d6f91649c2a</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 4 להעברה</t>
@@ -729,7 +729,7 @@
     <t>הכנת רצפה והגבהה יפורטו רק כשנדרשות בפרויקט. יש להגדיר גבול בין הכנת המשטח, איטום וריצוף, בלי לחייב אותה שכבה פעמיים. חומר, עומס ומפלסים ייקבעו בתכנון המאושר.</t>
   </si>
   <si>
-    <t>d739b3bc-780a-4a72-ba86-0ab69d5555d8</t>
+    <t>466a0621-8084-4e13-824b-06ae1f293800</t>
   </si>
   <si>
     <t>5.01</t>
@@ -738,7 +738,7 @@
     <t>ביצוע שכבת הכנה, מילוי או הגבהה באזור {אזור}, מחומר {מערכת}, בעובי ובמפלס {נתונים}, לרבות {תשתית, גמר והשלמות נכללים}, לפי פרט מאושר.</t>
   </si>
   <si>
-    <t>279664b5-0c3b-4d71-94ff-831a0ad7f0f2</t>
+    <t>2b141977-e021-40a8-8fd8-2bb1acf7ca3f</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 5 להעברה</t>
@@ -747,7 +747,7 @@
     <t>מערכת האיטום תיקבע לפי התשתית, השימוש, החדירות והמפגשים בפרויקט. כל סעיף יפרט את הכנת התשתית, סיומות, טיפול בנקזים ובפתחים ובדיקות נדרשות. אין ברירת מחדל לשיטת איטום, עובי, גובה רולקה או מותג.</t>
   </si>
   <si>
-    <t>0b2c232b-b1ec-4d04-9327-63c5c169d60b</t>
+    <t>f3209273-36ce-4d6a-ac79-bc18b5548b72</t>
   </si>
   <si>
     <t>6.01</t>
@@ -756,7 +756,7 @@
     <t>ביצוע איטום באזור רטוב {זיהוי ואזור}, במערכת {מפרט מאושר}, לרבות הכנת תשתית, מפגשי קיר ורצפה, חדירות וסיומות לפי הפרט. בדיקות ותכולת ההכנה: {פירוט}.</t>
   </si>
   <si>
-    <t>e3b5eca2-2a63-4dd4-9acb-ae3c70e63581</t>
+    <t>0f75327e-0b16-4fe7-8d77-a9961ba5cc1d</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 6 להעברה</t>
@@ -765,7 +765,7 @@
     <t>מחיר כל טיפוס דלת כולל כנף, משקוף, הלבשות, פרזול, גמר, הובלה והרכבה לפי תיאור הסעיף. סוגי מילוי, צירים, פתיחה והתאמת נגישות או בטיחות יוגדרו בפרויקט; אין הוראה כללית של פרזול הסותרת טיפוס דלת.</t>
   </si>
   <si>
-    <t>88b108a2-ba3a-44cb-b624-e7f2d477a59b</t>
+    <t>63ac9297-c59f-448c-9459-dd385c66d45d</t>
   </si>
   <si>
     <t>7.01</t>
@@ -775,7 +775,7 @@
 מידות ופתיחה: {מידות וכיוון}; כנף ומילוי: {מפרט}; משקוף והלבשות: {מפרט}; פרזול: {מפרט}; גמר וגוון: {מפרט}; תכנית ופרט: {הפניה}.</t>
   </si>
   <si>
-    <t>6af4c878-c16d-4cdc-b056-b9017d9ed215</t>
+    <t>e1d1d7bc-add2-4884-a3fb-2ba4ca89882f</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 7 להעברה</t>
@@ -784,7 +784,7 @@
     <t>מחירי עבודות הריצוף והחיפוי כוללים הכנת תשתית בתכולה שנקבעה, חומרי עזר, חיתוכים, התאמות, פינות ורובה בהתאם למפרט. אספקת האריחים תתומחר בפרק האספקות כשאינו כבוי; פנלים המופיעים בסעיף נפרד אינם כלולים שוב במחיר השטח.</t>
   </si>
   <si>
-    <t>035dd93f-ff8c-4c4f-82e0-fb95305e9064</t>
+    <t>35e5aa32-724f-47f4-92d6-cd9c196ae039</t>
   </si>
   <si>
     <t>8.01</t>
@@ -793,7 +793,7 @@
     <t>ריצוף חלל ציבורי ואזור ישיבה {אזור}, באריחי גרניט פורצלן שחור משופשף במידות 120×60 ס״מ, עם מישקים 2 מ״מ ורובה שחורה, על תשתית {סוג לפי הסניף}. אספקת האריחים {אחריות}; גמר מפגשים וסיומות לפי פרט {הפניה}.</t>
   </si>
   <si>
-    <t>e90f467b-62ad-4dc5-8390-2824cd47051d</t>
+    <t>1838623b-1265-4771-8b4f-14c4918d71a9</t>
   </si>
   <si>
     <t>8.02</t>
@@ -802,7 +802,7 @@
     <t>ריצוף שטח מטבח או דלפק הכנת מזון {אזור}, באריחי גרניט פורצלן אנטיסליפ במידות 30×30 ס״מ, עם מישקים 3 מ״מ ורובה שחורה. סוג הרובה ודרגת ההחלקה {אישור לפרויקט לפי OS-07}; טיפול במפגשים ובנקזים לפי פרט {הפניה}.</t>
   </si>
   <si>
-    <t>2a77b2b0-bd89-484c-aefa-7649237266a3</t>
+    <t>570f8e88-c1cf-4c28-91f2-76723bc2a3e6</t>
   </si>
   <si>
     <t>8.03</t>
@@ -811,7 +811,7 @@
     <t>חיפוי קירות ועמודים באזור {אזור}, באריחי גרניט פורצלן בגוון בטון משופשף במידות 120×60 ס״מ, לגובה {גובה}, עם מישקים 6 מ״מ ורובה טמבור אפור כהה 120. גמר פינות בגרונג. תשתית ואחריות אספקת האריחים {פירוט}; אין להחיל מידת אריח זו אוטומטית על דופן דלפק חתוכה.</t>
   </si>
   <si>
-    <t>529a5c22-b175-444b-a0a1-a79b20edce82</t>
+    <t>900d0ac8-48b8-4a8c-8e02-62dd1d546a3a</t>
   </si>
   <si>
     <t>8.04</t>
@@ -820,7 +820,7 @@
     <t>חיפוי דופן חיצונית קדמית של דלפק {זיהוי}, באריחי קרמיקה דקורטיבית משולבת פסי פליז, ללא פוגות, על תשתית {סוג}. מידות האריחים {מידות לפי הפרט}; במקורות מצוין 100×10 ס״מ עם אפשרות לשינוי, ולכן אינה מידה קבועה. פרופילי שלד וחיבוריהם מתומחרים בפרק המסגרות.</t>
   </si>
   <si>
-    <t>762c2a92-e28a-48bc-b6d4-aa7890919569</t>
+    <t>6e097459-54cc-492d-bc9c-d0c8168bf850</t>
   </si>
   <si>
     <t>8.05</t>
@@ -829,7 +829,7 @@
     <t>חיפוי דופן פנימית לדלפק {זיהוי}, באריחי קרמיקה שחורה, לגובה {גובה}, עם מישקים 2 מ״מ ורובה שחורה. מידות האריחים {בחירה לפרויקט לפי OS-03}; תשתית וגמר מפגשים {פרט}. אין לחייב שוב חיפוי פורמייקה באותו שטח.</t>
   </si>
   <si>
-    <t>f33b6302-5f9a-4646-afa0-50840c5212fb</t>
+    <t>dd5201ff-eb88-461a-8da5-e717ed909599</t>
   </si>
   <si>
     <t>8.06</t>
@@ -838,7 +838,7 @@
     <t>התקנת פנל תואם לריצוף {חומר וגמר}, בגובה {גובה}, לאורך האזור {אזור}, לרבות פינות וסיומות לפי הפרט.</t>
   </si>
   <si>
-    <t>814e0b35-7c45-4f2e-9d46-c65e831796f3</t>
+    <t>d67482ad-99ef-4b70-8543-9de3903af4d8</t>
   </si>
   <si>
     <t>ריצוף וחיפוי אושי־אושי (המשך)</t>
@@ -853,7 +853,7 @@
     <t>חיפוי קיר באזור {אזור}, באריחי גרניט פורצלן בגוון חלודה משופשף במידות 120×60 ס״מ, לגובה {גובה}, בשילוב פרופילים שקועים בגוון פליז ברוחב 2 ס״מ בפוגות, ורובה טמבור חום 105 בפוגות האנכיות; פינות בגרונג. תשתית ואחריות אספקת אריחים ופרופילים {פירוט}. אם הפרופילים מתומחרים בנפרד יש להחריגם כאן במפורש.</t>
   </si>
   <si>
-    <t>11915dd1-408c-46c9-8a03-20d139f5f017</t>
+    <t>0b47133c-479e-4989-9009-be435e0a1e7a</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 8 להעברה</t>
@@ -862,7 +862,7 @@
     <t>המחירים כוללים תשתית, תלייה, חיבורים, פרופילי גמר ופתחים למערכות לפי מפרט התקרה. יש להגדיר סוג לוח או אריח, גובה, טיפול אקוסטי וחיזוקים. גמר צבע מתומחר בנפרד אם אינו מפורש כחלק מהמוצר.</t>
   </si>
   <si>
-    <t>b018f255-7f74-4926-bd9d-03ca8de14c5f</t>
+    <t>5fe46611-2156-4845-a8ca-6de5a2968eac</t>
   </si>
   <si>
     <t>9.01</t>
@@ -871,7 +871,7 @@
     <t>ביצוע הנמכת תקרה באזור {אזור}, במערכת {סוג ושכבות}, בגובה {גובה}, לרבות התשתית, פתחים וחיזוקים המפורטים בתכנון.</t>
   </si>
   <si>
-    <t>90d00fb0-cde4-4ea7-96e7-6fb4866f2cbf</t>
+    <t>94a2f4c0-8a6c-40c7-8e0b-bd22f2c82024</t>
   </si>
   <si>
     <t>9.02</t>
@@ -880,7 +880,7 @@
     <t>ביצוע קרניז מטיפוס {טיפוס}, בחתך ובגובה {מידות}, באזור {אזור}, לרבות הכנה לתאורה או למיזוג לפי הפרט וללא אספקת גוף התאורה.</t>
   </si>
   <si>
-    <t>6931ce28-5fc3-4d9d-9a0a-6f3b1dcc9430</t>
+    <t>b92e9bbf-dbb1-4932-b6eb-ba05c41d1a6d</t>
   </si>
   <si>
     <t>9.03</t>
@@ -889,7 +889,7 @@
     <t>אספקה והתקנת תקרת מגשי פח ברוחב 30 ס״מ, בגמר לבן RAL 9010, עם פרופיל סיום L, באזור מטבח או מחסן {אזור}, לרבות תשתית, תלייה ופתחים לפי התכנון. גובה ועובי הפח {מפרט הסניף}.</t>
   </si>
   <si>
-    <t>a6e52682-36e0-454b-96bd-ee2696af011f</t>
+    <t>2548a76c-218d-4735-9c82-8595246435a4</t>
   </si>
   <si>
     <t>9.04</t>
@@ -898,7 +898,7 @@
     <t>אספקה והתקנת תקרה אקוסטית מסוג {סוג}, במודול ובגמר {מפרט}, באזור {אזור}, לרבות התשתית והחיבורים המתאימים כמפורט בתכנון.</t>
   </si>
   <si>
-    <t>bbacb34f-969a-4784-82e4-352b2d5757d0</t>
+    <t>200d153c-3880-422c-be48-186932574514</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 9 להעברה</t>
@@ -907,7 +907,7 @@
     <t>עבודות הצבע כוללות תיקונים, החלקה וחומרי יסוד לפי המשטח והוראות המוצר. שלושה גמרי קיר מתומחרים בנפרד: נישה באפור טמבור 1537T; קירות מחסן בלבן; טיח אפקט בטון משופשף טמבור 440 לקירות או עמודים שסומנו כך בתכנון. תקרות גבס וקרניזים שחורים לפי הסעיף הנפרד. אין להחיל גוון אחד על כל המשטחים ואין להעתיק הוראות דילול ישנות.</t>
   </si>
   <si>
-    <t>65d9619e-f59f-4ffb-979d-4f212dc38e6e</t>
+    <t>ff4fda8e-44ca-4e66-aea4-8586cf037eee</t>
   </si>
   <si>
     <t>10.01</t>
@@ -916,7 +916,7 @@
     <t>הכנת וצביעת נישה או קטע קיר מסומן באזור {אזור}, לרבות תיקוני תשתית והחלקה, בצבע אקרילי מסוג סופרקריל בשתי שכבות לפחות ועד כיסוי מלא, בגוון אפור טמבור 1537T. חומר יסוד לפי המשטח והוראות המוצר.</t>
   </si>
   <si>
-    <t>57de838b-c1ff-4814-8a3e-fc2ecf82c909</t>
+    <t>aa7c38e3-7c39-4609-b349-3201da5ef546</t>
   </si>
   <si>
     <t>10.02</t>
@@ -925,7 +925,7 @@
     <t>הכנת וצביעת תקרות גבס והנמכות באזור {אזור}, לרבות תיקוני תשתית ושפכטל אמריקאי עד החלקה, בצבע אקרילי מסוג סופרקריל בשתי שכבות לפחות ועד כיסוי מלא, בגוון שחור. קוד גוון וברק {אישור לפי OS-04}; חומר יסוד לפי המשטח והוראות המוצר. אין לכלול כאן גמר מפעלי של תקרת המגשים.</t>
   </si>
   <si>
-    <t>5249fb67-2ebb-416a-85de-0aeb02b82fc1</t>
+    <t>11ede202-65ea-42e0-ae43-ec839b1b841b</t>
   </si>
   <si>
     <t>10.03</t>
@@ -934,7 +934,7 @@
     <t>ביצוע טיח דקורטיבי אפקט בטון משופשף של טמבור, בגוון 440, על קירות או עמודים מסומנים באזור {אזור}, בשתי שכבות לפחות ועד כיסוי מלא, לרבות הכנת תשתית ושפכטל עד החלקה לפי המשטח והוראות המוצר.</t>
   </si>
   <si>
-    <t>7c779bf6-5dc8-491e-a313-8a6ae8be25bd</t>
+    <t>a62c4017-3217-41f3-8aad-89716a35cb01</t>
   </si>
   <si>
     <t>10.04</t>
@@ -943,7 +943,7 @@
     <t>הכנת וצביעת קירות מחסן {זיהוי}, לרבות תיקוני תשתית והכנת משטח, בצבע אקרילי מסוג סופרקריל בשתי שכבות לפחות ועד כיסוי מלא, בגוון לבן. חומר יסוד לפי המשטח והוראות המוצר.</t>
   </si>
   <si>
-    <t>1a5045ec-62d9-4b53-bf57-e987bd4be60d</t>
+    <t>b3854162-78a5-4760-9ff7-64b9eca3316c</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 10 להעברה</t>
@@ -952,7 +952,7 @@
     <t>מחיר כל פריט נגרות כולל חומרים, פרזול, גמר, הובלה והרכבה שפורטו. מפרט רכיבי אלון: לוחות עץ לבוד מצופים פורניר אלון שטרייף ועץ מסיבי אלון; גמר לכה מט משי 15% ברק. ברכיבי פורמייקה: פורמקס 3199. גוון הבייץ 1067 GV; אין להחליף את האלון או דגם הפורמייקה בשדה חומר כללי. מתכת, משטחים מיוחדים, זיגוג וציוד בסעיפים נפרדים מוחרגים.</t>
   </si>
   <si>
-    <t>e6d6b168-577f-48a1-a785-79c9ce0a98c3</t>
+    <t>c7c452c8-034b-4325-ad1e-b6c72cd84fd5</t>
   </si>
   <si>
     <t>11.01</t>
@@ -961,7 +961,7 @@
     <t>אספקה והתקנת משטח הגשה ואכילה לדלפק {זיהוי}, מעץ מסיבי אלון בעובי 2 ס״מ, עם קנט קדמי 8 ס״מ וקנט אחורי 4 ס״מ, בגמר לכה מט משי 15% ברק. בייץ 1067 GV; אורך, רוחב, צורה וגובה התקנה {מידות סניף}. שלד, דפנות ומשטחים מיוחדים בסעיפים נפרדים אינם כלולים.</t>
   </si>
   <si>
-    <t>505199b7-23f9-46a5-bae6-2ec608970020</t>
+    <t>314a0c16-a1bb-446f-bbdd-3516edb578da</t>
   </si>
   <si>
     <t>11.02</t>
@@ -970,7 +970,7 @@
     <t>אספקה והתקנת דופן פנימית לדלפק {זיהוי}, בגובה ובעובי {מידות}, על תשתית {סוג}, לרבות פתחים והתאמות לציוד. גמר נבחר {חיפוי קרמי לפי פרק ריצוף או פורמייקה פורמקס 3199 לפי פרט הסניף}; יש להשאיר בחירה אחת. בחיפוי קרמי הנגרות כוללת תשתית בלבד והחיפוי מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>72e7ba87-dc88-46de-9b6c-263b6f8a03c2</t>
+    <t>1284b05b-d161-4cbd-9bd4-517f508ac88a</t>
   </si>
   <si>
     <t>11.03</t>
@@ -979,7 +979,7 @@
     <t>אספקה והתקנת חיפוי נגרות גלוי לדלפק {זיהוי}, רק בשטח המסומן לנגרות בפרט, מלוחות עץ לבוד מצופים פורניר אלון שטרייף ועץ מסיבי אלון לפי המפרט המשותף, בגמר לכה מט משי 15% ברק ובייץ 1067 GV. גובה וחלוקה {מידות}; בשטח המיועד לקרמיקה יש לתמחר תשתית בלבד בסעיף התשתית, ללא חיפוי אלון נוסף.</t>
   </si>
   <si>
-    <t>c3cd28e5-5d01-4c10-8fa1-6eb41b02e3cb</t>
+    <t>a2a5f016-b272-4556-804c-9a598da427b3</t>
   </si>
   <si>
     <t>11.04</t>
@@ -988,7 +988,7 @@
     <t>אספקה והתקנת שער או דלת כניסה לדלפק מטיפוס {טיפוס}, במידות {מידות}, מחומר ובגמר {מפרט}, לרבות מסגרת, צירים, סגירה וחיבורים כפי שנקבעו בפרט.</t>
   </si>
   <si>
-    <t>dc27ed35-c9b3-444b-a671-043c55df5ff9</t>
+    <t>3d946359-6da5-478a-badd-081bc2ba3fb3</t>
   </si>
   <si>
     <t>11.05</t>
@@ -997,7 +997,7 @@
     <t>התקנת לוחות תשתית לדופן דלפק {זיהוי}, מחומר ובעובי {מפרט}, על גבי {תשתית}, כהכנה לחיפוי {חומר}. החיפוי הסופי מתומחר בפרק הריצוף והחיפוי או בפרק המשטחים.</t>
   </si>
   <si>
-    <t>fb19eebb-f858-4a25-81c9-76315e81b53b</t>
+    <t>80cd262b-465a-4ccd-9cda-c7285cfef908</t>
   </si>
   <si>
     <t>11.06</t>
@@ -1006,7 +1006,7 @@
     <t>אספקה והתקנת יחידת מדפים או בר תצוגה אחורי {זיהוי}, מלוחות עץ לבוד בגמר פורניר אלון שטרייף, עם קנטים קדמיים מעץ מסיבי אלון, בגמר לכה מט משי 15% ברק ובייץ 1067 GV. מידות, חלוקה וחתך קנט {מפרט סניף}. מסגרות התמיכה והמראות מתומחרות בנפרד.</t>
   </si>
   <si>
-    <t>d9d2e282-ac14-48e1-977b-b51cf959cf46</t>
+    <t>2ddb3181-1b11-471e-9105-3351f2332baa</t>
   </si>
   <si>
     <t>נגרות אושי־אושי (המשך)</t>
@@ -1018,7 +1018,7 @@
     <t>אספקה והתקנת עמדת מלצרים מטיפוס {טיפוס}, במידות {מידות}, הכוללת ארון, חלוקה פנימית, דלתות ומגירות {פירוט}; חומרי פנים וחוץ, גמר ופרזול {מפרט}.</t>
   </si>
   <si>
-    <t>7ca31fc3-ad79-4d9c-af85-8438db16427e</t>
+    <t>dafbd9d0-14a8-4c28-bcf1-c3c71c56d838</t>
   </si>
   <si>
     <t>11.08</t>
@@ -1027,7 +1027,7 @@
     <t>אספקה והתקנת עמדת משלוחים מטיפוס {טיפוס}, במידות {מידות}, מחומרים ובגמר {מפרט}, לרבות חלוקה פנימית, פרזול ופתחים המוגדרים לפריט.</t>
   </si>
   <si>
-    <t>6f64ed20-35c0-4c0c-ae0e-6bfddc26600c</t>
+    <t>2cbaad5d-fa81-4afe-875b-c926b41bfc2d</t>
   </si>
   <si>
     <t>11.09</t>
@@ -1036,13 +1036,13 @@
     <t>אספקה והתקנת ארון שירות מטיפוס {טיפוס}, במידות {מידות}, בחלוקה {חלוקה}, מחומרים ובגמר {מפרט}, לרבות פרזול וחיבורים. משטח עליון מתומחר בנפרד בפרק המשטחים.</t>
   </si>
   <si>
-    <t>e4142fab-622c-4c97-8e40-155fc06a2ee6</t>
+    <t>9697302d-8585-44b5-8562-dd6046e1a8e6</t>
   </si>
   <si>
     <t>מפרט משותף לפלטות שולחן: תשתית {חומר}, גמר עליון ותחתון {מפרט}, קנט {מפרט}, הכנות וחיבור לרגל {מפרט}. כל גודל או טיפוס בתמחור שונה יופיע כסעיף עצמאי. המידות אינן ערכי ברירת מחדל.</t>
   </si>
   <si>
-    <t>c07c12c9-f785-4ac9-ba64-8c3dd32fd7a1</t>
+    <t>cde0afea-e4ef-4775-9bdf-bc12b3754800</t>
   </si>
   <si>
     <t>11.10</t>
@@ -1051,7 +1051,7 @@
     <t>פלטת שולחן מטיפוס {טיפוס א}, במידות {מידות א}, לפי המפרט המשותף, לרבות {תכולת הכנות וחיבור}.</t>
   </si>
   <si>
-    <t>f6272e14-b96a-4269-8f83-fe57fa052f79</t>
+    <t>f1d2acc2-0836-4bf8-8fae-ebb2d4a18571</t>
   </si>
   <si>
     <t>11.11</t>
@@ -1060,7 +1060,7 @@
     <t>פלטת שולחן מטיפוס {טיפוס ב}, במידות {מידות ב}, לפי המפרט המשותף, לרבות {תכולת הכנות וחיבור}.</t>
   </si>
   <si>
-    <t>1d16f450-db46-4817-83ae-c4be601a2593</t>
+    <t>a51d5e6d-6622-40ae-9c64-47e2ff9dd120</t>
   </si>
   <si>
     <t>11.12</t>
@@ -1069,7 +1069,7 @@
     <t>פלטת שולחן מטיפוס {טיפוס ג}, במידות {מידות ג}, לפי המפרט המשותף, לרבות {תכולת הכנות וחיבור}.</t>
   </si>
   <si>
-    <t>1c434242-36b3-40c9-9d75-9f3d2131bdd2</t>
+    <t>0b0a7863-bedc-4c8d-bad6-a8dedfe73fec</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 11 להעברה</t>
@@ -1078,7 +1078,7 @@
     <t>עבודות המסגרות כוללות חומרי גלם, חיבורים, עיגון, הכנת שטח, צבע יסוד וגמר, הובלה והרכבה. שני גמרים מאושרים: שחור מט RAL 9005 וזהב מושחר RAL 1036. כל טיפוס מופיע בסעיף נפרד לכל גמר לצורך תמחור; ממלאים רק את הפריטים והגמרים הנדרשים בסניף ואין לחייב את שניהם לאותו רכיב. חתכים, עוביים, עיגון ותלייה לפי תכנון. נגרות, זכוכית ותאורה בסעיפים נפרדים מוחרגות.</t>
   </si>
   <si>
-    <t>ede56674-a0e0-4594-b46c-35708807b906</t>
+    <t>fa095c4a-4c90-4463-bfb4-682e0ca9062b</t>
   </si>
   <si>
     <t>12.01</t>
@@ -1087,7 +1087,7 @@
     <t>אספקה והתקנת שלד מסגרות לדלפק {זיהוי}, מפרופילי ברזל {חתך ועובי לפי תכנון}, בגמר שחור מט RAL 9005, בגובה ובחלוקה {מידות}, לרבות עיגון והכנות למעבר תשתיות. נגרות, אריחים ומשטחים בסעיפים נפרדים אינם כלולים.</t>
   </si>
   <si>
-    <t>a91a7af2-dc99-450d-b0f0-e514181f4b96</t>
+    <t>b0494e87-dac8-43bc-a9b5-90bd179dbc6e</t>
   </si>
   <si>
     <t>12.02</t>
@@ -1096,7 +1096,7 @@
     <t>אספקה והתקנת יחידת מדפי מתכת או מתקן תצוגה {טיפוס}, מפרופילי ברזל ומשטחים {חתכים ועוביים לפי תכנון}, בגמר שחור מט RAL 9005, במידות {מידות}, לרבות תלייה ועיגון {מפרט}. אין לכלול כאן פריט זהה בגמר זהב מושחר המתומחר בסעיף נפרד.</t>
   </si>
   <si>
-    <t>6ac9c51a-c10d-4be4-a589-8ecbdee65bc9</t>
+    <t>eaa91bda-8631-41e4-ade6-045109456fa7</t>
   </si>
   <si>
     <t>12.03</t>
@@ -1105,7 +1105,7 @@
     <t>אספקה והתקנת מסגרת ברזל לתמיכת פריט {זיהוי}, בגמר שחור מט RAL 9005, במידות ובחתכים {מפרט תכנון}, לרבות עיגון והכנות {פירוט}. הפריט הנתמך מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>e2972e79-9c46-48b0-90cc-f830e3330095</t>
+    <t>c8bd28b8-ef06-41c4-b18d-dd6a6504429c</t>
   </si>
   <si>
     <t>12.04</t>
@@ -1114,7 +1114,7 @@
     <t>אספקה והתקנת מחיצה או מסגרת דקורטיבית מברזל, בגמר שחור מט RAL 9005, באזור {אזור}, במידות, בחתכים ובחלוקה {מפרט תכנון}. מילוי נגרות, אריחים או זכוכית מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>94c849cd-cf94-40cb-a323-fc827fb7177d</t>
+    <t>330a2b4f-4ccf-4ed0-88e6-20c23dfeca96</t>
   </si>
   <si>
     <t>12.05</t>
@@ -1123,7 +1123,7 @@
     <t>אספקה והתקנת מסגרת ברזל תומכת לשילוט בהיקף דלפק {זיהוי}, בגמר שחור מט RAL 9005, במידות ובפרופילים {מפרט תכנון}, לרבות עיגון והכנה למעבר הזנה. אותיות, תאורה ושלט הגמר מתומחרים בנפרד.</t>
   </si>
   <si>
-    <t>9c0d69cf-954b-4d90-80d9-eef1f2aa6d8a</t>
+    <t>c92f7217-8246-47b5-9497-9db6a7420a18</t>
   </si>
   <si>
     <t>12.06</t>
@@ -1132,7 +1132,7 @@
     <t>אספקה והתקנת שלד מסגרות לדלפק {זיהוי}, מפרופילי ברזל {חתך ועובי לפי תכנון}, בגמר זהב מושחר RAL 1036, בגובה ובחלוקה {מידות}, לרבות עיגון והכנות למעבר תשתיות. נגרות, אריחים ומשטחים בסעיפים נפרדים אינם כלולים.</t>
   </si>
   <si>
-    <t>be913337-5e8d-4009-8a1b-7543b0addea3</t>
+    <t>086f6518-8b58-4b13-9450-e1f942c8b2a9</t>
   </si>
   <si>
     <t>מסגרות אושי־אושי (המשך)</t>
@@ -1144,7 +1144,7 @@
     <t>אספקה והתקנת יחידת מדפי מתכת או מתקן תצוגה {טיפוס}, מפרופילי ברזל ומשטחים {חתכים ועוביים לפי תכנון}, בגמר זהב מושחר RAL 1036, במידות {מידות}, לרבות תלייה ועיגון {מפרט}. אין לכלול כאן פריט זהה בגמר שחור המתומחר בסעיף נפרד.</t>
   </si>
   <si>
-    <t>6d89502a-e2d8-4d8f-8c15-91e7883b0455</t>
+    <t>4f1f2684-8a1d-48b8-ac20-8e8db4dbb59a</t>
   </si>
   <si>
     <t>12.08</t>
@@ -1153,7 +1153,7 @@
     <t>אספקה והתקנת מסגרת ברזל לתמיכת פריט {זיהוי}, בגמר זהב מושחר RAL 1036, במידות ובחתכים {מפרט תכנון}, לרבות עיגון והכנות {פירוט}. הפריט הנתמך מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>98ed4f35-d46a-47fc-b06a-06e1cbf28e04</t>
+    <t>f31152df-c05a-4c0e-89a9-4aa9748cda46</t>
   </si>
   <si>
     <t>12.09</t>
@@ -1162,7 +1162,7 @@
     <t>אספקה והתקנת מחיצה או מסגרת דקורטיבית מברזל, בגמר זהב מושחר RAL 1036, באזור {אזור}, במידות, בחתכים ובחלוקה {מפרט תכנון}. מילוי נגרות, אריחים או זכוכית מתומחר בנפרד.</t>
   </si>
   <si>
-    <t>a02b0c22-f069-471d-aac4-106aec900ad0</t>
+    <t>222656ae-b086-4f27-a513-39f7961e14cf</t>
   </si>
   <si>
     <t>12.10</t>
@@ -1171,7 +1171,7 @@
     <t>אספקה והתקנת מסגרת ברזל תומכת לשילוט בהיקף דלפק {זיהוי}, בגמר זהב מושחר RAL 1036, במידות ובפרופילים {מפרט תכנון}, לרבות עיגון והכנה למעבר הזנה. אותיות, תאורה ושלט הגמר מתומחרים בנפרד.</t>
   </si>
   <si>
-    <t>7bc1bad8-a136-40ed-a037-d1a04cc009a2</t>
+    <t>dd8305f9-3647-4580-a410-6624bb3a9066</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 12 להעברה</t>
@@ -1180,7 +1180,7 @@
     <t>כל טיפוס פתח או זיגוג יפורט לפי מידות, שימוש, פרופיל, סוג ועובי זכוכית, פרזול וגמר. אין ברירת מחדל לסדרת פרופיל, עובי זכוכית או שיטת עיגון. רכיב מתומחר כאן לא ייכלל שוב במפרט נגרות או מסגרות.</t>
   </si>
   <si>
-    <t>1ea82966-c69b-4c57-ab84-7be26dd80dd7</t>
+    <t>1ef068b8-bfee-4478-9d47-4b705e3a1eed</t>
   </si>
   <si>
     <t>13.01</t>
@@ -1190,7 +1190,7 @@
 סוג פתיחה וחלוקה: {מפרט}; פרופיל וגמר: {מפרט}; זיגוג: {סוג ועובי}; פרזול, אטימה וסיומות: {מפרט}; פרט: {הפניה}.</t>
   </si>
   <si>
-    <t>99cb4301-2cf4-4688-afe7-32f8d8fbde3d</t>
+    <t>3bf875f0-b047-4a1c-b2aa-2997cce118ac</t>
   </si>
   <si>
     <t>13.02</t>
@@ -1199,7 +1199,7 @@
     <t>אספקה והתקנת לוח זיגוג מטיפוס {זיהוי}, במידות {מידות}, בסוג ובעובי {מפרט}, לרבות חיבורים ופרזול שנקבעו לפרט. שלד המסגרת מתומחר בנפרד ככל שהוגדר בפרק המסגרות.</t>
   </si>
   <si>
-    <t>fefbffb3-a85b-4be5-9251-ca172d4de6bf</t>
+    <t>2d3467f9-77ec-489a-a2d9-137eb72cdeb8</t>
   </si>
   <si>
     <t>13.03</t>
@@ -1208,7 +1208,7 @@
     <t>אספקה והתקנת מראה מטיפוס {זיהוי}, במידות ובצורה {מידות}, בסוג ובעובי {מפרט}, עם גמר קצה וחיבור {פירוט}. מסגרת ותאורה נכללות רק אם צוינו במפורש.</t>
   </si>
   <si>
-    <t>c4175152-e8a6-406f-8bda-4c454e4f5583</t>
+    <t>80b61e81-d496-453b-a802-d9da6490201b</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 13 להעברה</t>
@@ -1217,7 +1217,7 @@
     <t>מחירי המשטחים כוללים עיבוד, חיתוכים, פתחים, קנטים, הובלה והרכבה רק כפי שהוגדרו בפריט. חומר, דגם, עובי וחתך הם משתני פרויקט. אותו משטח לא ייכלל שוב במחיר הנגרות או הציוד.</t>
   </si>
   <si>
-    <t>0211a3d5-ce4e-46cb-82c0-2b1d9cfa8562</t>
+    <t>aa64a5c3-1fde-4a02-855d-db6bcc40b63a</t>
   </si>
   <si>
     <t>14.01</t>
@@ -1226,7 +1226,7 @@
     <t>אספקה והתקנת משטח עבודה עבור {פריט}, מחומר ודגם {מפרט}, ברוחב ובעובי {מידות}, לרבות פתחים, קנטים וחיבורים {פירוט}, על תשתית {סוג}.</t>
   </si>
   <si>
-    <t>4e57bc45-072e-4150-b60e-fd86cf1d2ef8</t>
+    <t>4da5fed6-9025-45f6-8b18-262526c07257</t>
   </si>
   <si>
     <t>14.02</t>
@@ -1235,7 +1235,7 @@
     <t>אספקה והתקנת קופינג או צוקל לדלפק או למחיצה {זיהוי}, מחומר ודגם {מפרט}, בחתך {מידות}, עם פינות, קנטים וחיבורים {פירוט}.</t>
   </si>
   <si>
-    <t>83e364dc-1b36-4b81-a311-5d68d8e524f2</t>
+    <t>0f377f48-8b6a-41a2-b9ea-1ba1333d5643</t>
   </si>
   <si>
     <t>14.03</t>
@@ -1244,7 +1244,7 @@
     <t>אספקה והתקנת משטח כיור לארון {זיהוי}, במידות {מידות}, מחומר ודגם {מפרט}, עם פתחים, קנטים וחיבור {פירוט}. כיור וברז: {כלולים או מוחרגים במפורש}.</t>
   </si>
   <si>
-    <t>11c7765a-0e84-4cbf-89f1-f330a0932a0f</t>
+    <t>2023545f-de8c-4a30-ac50-27d62cddb5de</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 14 להעברה</t>
@@ -1253,7 +1253,7 @@
     <t>פרק אספקות נפתח רק כשהאספקה נפרדת מהתקנה. מפרטי האריחים, הגוונים והגמרים בשורות הרשת חלים גם על האספקה המקבילה; אין לפתוח שוב בחירה חופשית במקום מפרט שנקבע. במקורות אין דגם גוף תאורה משותף ומלא לרשת: OS-08. כל טיפוס אספקה בעל תמחור שונה יקבל סעיף עצמאי. אין כמויות רכש או פחת בתבנית.</t>
   </si>
   <si>
-    <t>05e0039a-1dac-4677-95a7-679d514b9228</t>
+    <t>42b64bf1-81a5-4fc1-b144-3cddd79145c2</t>
   </si>
   <si>
     <t>15.01</t>
@@ -1262,7 +1262,7 @@
     <t>אספקת אריחי ריצוף או חיפוי מטיפוס {זיהוי}, מחומר ודגם {מפרט}, במידה ובגמר {מפרט}. הובלה ופריקה: {תכולה}; התקנה מתומחרת בנפרד.</t>
   </si>
   <si>
-    <t>d79791c7-a25c-413d-af24-d032985ea078</t>
+    <t>55fa57c7-5102-40fd-90da-42b9f2068bb2</t>
   </si>
   <si>
     <t>15.02</t>
@@ -1271,7 +1271,7 @@
     <t>אספקת כלי או אביזר סניטרי מטיפוס {זיהוי}, בדגם ובגמר {מפרט}, לרבות {אביזרים נלווים}. התקנה וחיבור מתומחרים בפרק האינסטלציה.</t>
   </si>
   <si>
-    <t>41ea2e75-51bf-4b18-86a4-c3a2d83568a1</t>
+    <t>2ea98e58-f874-4df7-833e-40ed1151d327</t>
   </si>
   <si>
     <t>15.03</t>
@@ -1280,7 +1280,7 @@
     <t>אספקת גוף תאורה מטיפוס {זיהוי}, במפרט ובדגם {מפרט}, עם {ספק, דרייבר ואביזרים נלווים לפי הנדרש}. התקנה ונקודת הזנה מתומחרות בפרק החשמל.</t>
   </si>
   <si>
-    <t>f7ba6162-7a3c-409e-9652-9d29de9cd080</t>
+    <t>a2f5b446-8f69-4c32-a95f-d74ed018a127</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 15 להעברה</t>
@@ -1289,7 +1289,7 @@
     <t>תוכן מערכת זו יושלם בפרויקט לפי תכנון היועץ ורשימת הציוד המאושרים. שורות התבנית מגדירות גבולות תכולה ואינן מפרט הנדסי מלא. אין להסיק מהפעלת הפרק שהמערכת נדרשת בכל אתר.</t>
   </si>
   <si>
-    <t>a6b1da0d-28be-4b30-939d-973a7d8c8ccf</t>
+    <t>03e87163-14de-4ff4-9b63-6183c8882f4b</t>
   </si>
   <si>
     <t>16.01</t>
@@ -1298,13 +1298,13 @@
     <t>ביצוע מערכת מיזוג ואוורור בתכולת {מערכת מוגדרת}, לפי תכנון {הפניה}, לרבות {אספקה, התקנה, חיבור והפעלה}. גבולות מול חשמל, ניקוז ותקרות: {פירוט}.</t>
   </si>
   <si>
-    <t>4430e329-d945-41f7-a764-feb500d143c7</t>
+    <t>cc25561a-8006-4171-80c2-b2d42d5f15b7</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 16 להעברה</t>
   </si>
   <si>
-    <t>bebd7028-32ab-4e90-9cae-d17a27cbacdc</t>
+    <t>b49ae10f-91d0-4711-9d26-53ec6031d7ff</t>
   </si>
   <si>
     <t>17.01</t>
@@ -1313,7 +1313,7 @@
     <t>אספקה והתקנת פריט ציוד מטבח או נירוסטה {זיהוי}, לפי רשימת ציוד {הפניה}, בתכולת {מפרט}, עם גבולות חיבור למערכות {פירוט}.</t>
   </si>
   <si>
-    <t>bd805dde-5240-4b77-ad6f-adb0d8432d13</t>
+    <t>29fac985-8557-4545-aeea-e98df925979f</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 17 להעברה</t>
@@ -1322,7 +1322,7 @@
     <t>מערכת הגז נפתחת רק כשנדרשת בתכנון הפרויקט. תשתית, אביזרים, בדיקות וגבולות חיבור ייקבעו במפרט המתכנן והגורם המבצע; אין הנחת סוג צנרת, צובר קיים או מיקום ציוד מהארכיון.</t>
   </si>
   <si>
-    <t>cf1f2c8b-f851-4583-bee3-355c9d5508ff</t>
+    <t>f4677fe2-94a7-4b2c-8a28-ac354fff9754</t>
   </si>
   <si>
     <t>18.01</t>
@@ -1331,13 +1331,13 @@
     <t>ביצוע נקודת גז עבור {ציוד מזוהה}, לפי תכנון {הפניה}, לרבות התשתית ואביזרי החיבור בתכולת {מפרט}. גבולות אחריות אספקת המערכת, חיבור הציוד ובדיקות: {פירוט}.</t>
   </si>
   <si>
-    <t>f37a71cd-2251-46bf-a7f4-f9a14e3dbe6f</t>
+    <t>136d92f1-3993-4801-becf-ca6acb7f956a</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 18 להעברה</t>
   </si>
   <si>
-    <t>080669c8-5251-411c-a0cf-4d05eaf25115</t>
+    <t>bd3a46f2-c266-4b6a-85fe-a61e73609c47</t>
   </si>
   <si>
     <t>19.01</t>
@@ -1346,7 +1346,7 @@
     <t>ביצוע מערכת כיבוי {סוג מערכת מוגדר}, לפי תכנון בטיחות וכיבוי {הפניה}, בגבולות {תכולה ואחריות}, עם הממשקים למערכות האחרות כמפורט.</t>
   </si>
   <si>
-    <t>3d054596-1420-40d4-a88b-ed47366d45f6</t>
+    <t>5336b120-3c66-4cb9-bbd6-5be324f9a39c</t>
   </si>
   <si>
     <t>19.02</t>
@@ -1355,7 +1355,7 @@
     <t>ביצוע מערכת גילוי או התרעה {סוג מערכת מוגדר}, לפי תכנון {הפניה}, בגבולות {תכולה ואחריות}, עם ההכנות והחיבורים המפורטים.</t>
   </si>
   <si>
-    <t>107122bc-7559-4a35-aa88-0f04c5ac4ced</t>
+    <t>12a85cbe-935c-4c27-b2e3-20141cbdff48</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 19 להעברה</t>
@@ -1364,7 +1364,7 @@
     <t>אביזרי נגישות יוגדרו לפי תכנון הנגישות בפרויקט. אין להעתיק מידות, מיקום או רשימת אביזרים מתיק אחר. האביזרים אינם כלולים שוב במחיר מכל ההדחה או הנגרות.</t>
   </si>
   <si>
-    <t>48aa3c72-d099-44cc-94af-690fe47fbbf6</t>
+    <t>3e79e6a9-c603-42b5-888a-b35ece603bf0</t>
   </si>
   <si>
     <t>20.01</t>
@@ -1373,13 +1373,13 @@
     <t>אספקה והתקנת ערכת אביזרי נגישות לחדר שירות {זיהוי}, הכוללת {רשימה מאושרת של אביזרים}, בחומרים, במידות ובמיקומים לפי תכנון {הפניה}, לרבות העיגון המוגדר.</t>
   </si>
   <si>
-    <t>bff4b214-9be8-46d8-849c-8aea60c0700f</t>
+    <t>56baad86-dc2b-4109-8635-d03819f35de7</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 20 להעברה</t>
   </si>
   <si>
-    <t>7427a35d-c54b-4cac-8b50-59f437a2794d</t>
+    <t>e2e66179-3668-4d9d-9f89-e126fe016753</t>
   </si>
   <si>
     <t>21.01</t>
@@ -1388,7 +1388,7 @@
     <t>אספקה והתקנת שילוט או אותיות מטיפוס {זיהוי}, במידות ובחומר {מפרט}, בגמר {גמר}, לרבות {תאורה, ספק, פרזול והתקנה}. תשתית והזנה מתומחרות בנפרד אם צוינו בפרק החשמל.</t>
   </si>
   <si>
-    <t>91ab0439-3352-4b64-a5ca-14e972a80379</t>
+    <t>ea5e50ce-89d0-4beb-9cf1-c103877e25c6</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 21 להעברה</t>
@@ -1397,7 +1397,7 @@
     <t>מחיר כל פריט נגרות כולל את החומרים, החיפויים, הפרזול, הגמר, ההובלה וההרכבה שפורטו בסעיף. רכיבי מתכת, משטחי אבן או חומר מיוחד, זיגוג וציוד שמופיעים בפרק נפרד מוחרגים ממחיר הנגרות. מידות, גוונים ודגמים יושלמו לכל פריט.</t>
   </si>
   <si>
-    <t>88841134-2c8c-417b-8acc-6af740ad63ab</t>
+    <t>fd7777c9-30f0-4ed3-a58c-3afb7aa6c74e</t>
   </si>
   <si>
     <t>22.01</t>
@@ -1406,7 +1406,7 @@
     <t>אספקה והתקנת ספת ישיבה קבועה מטיפוס {זיהוי}, במידות ובחתך {מידות}, עם שלד, ריפוד וגמר {מפרט}, לרבות עיגון ותכולה {פירוט}.</t>
   </si>
   <si>
-    <t>7e283deb-a816-4e49-8ff9-9746925aaea4</t>
+    <t>eb27c2bf-90cf-48a8-82dd-80c2554e74a5</t>
   </si>
   <si>
     <t>22.02</t>
@@ -1415,7 +1415,7 @@
     <t>אספקת פריט ריהוט נייד מטיפוס {זיהוי}, בדגם ובגמר {מפרט}, לרבות {הובלה והרכבה}.</t>
   </si>
   <si>
-    <t>ac68329b-2b1b-4798-a718-ec48d7b8138e</t>
+    <t>522865dc-2d1d-4631-af4e-664495d739e8</t>
   </si>
   <si>
     <t>סיכום חלקי פרק 22 להעברה</t>
@@ -1437,12 +1437,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;תאריך: &quot;@"/>
     <numFmt numFmtId="165" formatCode="&quot;פרק &quot;0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    <numFmt numFmtId="167" formatCode="[=0]#,##0&quot;₪&quot;;#,##0.00&quot;₪&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;₪&quot;"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1656,7 +1654,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1682,10 +1680,10 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
@@ -1694,1394 +1692,31 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="454">
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="#,##0&quot;₪&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00&quot;₪&quot;"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3723,30 +2358,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="148" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="149" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="150" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="151" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="152" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -4097,126 +2708,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B16:E16"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="154" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="155" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="156" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="158" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="159" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="160" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="162" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="164" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="166" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="168" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="169" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="170" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="171" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="172" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="174" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="175" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="176" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="177" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="178" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="179" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="180" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="expression" dxfId="182" priority="1">
-      <formula>AND(ISNUMBER(F16),ROUND(F16,2)=INT(ROUND(F16,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="183" priority="2">
-      <formula>AND(ISNUMBER(F16),ROUND(F16,2)&lt;&gt;INT(ROUND(F16,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D13">
       <formula1>0</formula1>
@@ -4457,78 +2948,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B9:E9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="184" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="185" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="186" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="187" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="188" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="189" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="190" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="191" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="192" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="193" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="194" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="195" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="196" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="197" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="198" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="199" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="200" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="201" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D7">
       <formula1>0</formula1>
@@ -4754,78 +3173,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B9:E9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="202" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="203" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="204" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="206" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="207" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="208" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="209" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="210" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="211" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="212" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="213" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="214" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="215" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="216" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="217" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="218" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="219" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D7">
       <formula1>0</formula1>
@@ -5304,206 +3651,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B21:E21"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="220" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="221" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="222" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="223" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="224" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="225" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="226" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="227" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="228" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="229" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="230" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="231" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="232" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="233" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="234" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="235" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="236" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="237" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="238" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="239" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="240" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="241" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="242" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="243" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="244" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="245" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="246" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="247" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="expression" dxfId="248" priority="1">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)=INT(ROUND(E14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="249" priority="2">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)&lt;&gt;INT(ROUND(E14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="250" priority="1">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)=INT(ROUND(F14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="251" priority="2">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)&lt;&gt;INT(ROUND(F14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="expression" dxfId="252" priority="1">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)=INT(ROUND(E15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="253" priority="2">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)&lt;&gt;INT(ROUND(E15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="254" priority="1">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)=INT(ROUND(F15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="255" priority="2">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)&lt;&gt;INT(ROUND(F15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="256" priority="1">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)=INT(ROUND(E17,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="257" priority="2">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)&lt;&gt;INT(ROUND(E17,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="258" priority="1">
-      <formula>AND(ISNUMBER(F17),ROUND(F17,2)=INT(ROUND(F17,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="259" priority="2">
-      <formula>AND(ISNUMBER(F17),ROUND(F17,2)&lt;&gt;INT(ROUND(F17,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="expression" dxfId="260" priority="1">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)=INT(ROUND(E18,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="261" priority="2">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)&lt;&gt;INT(ROUND(E18,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="expression" dxfId="262" priority="1">
-      <formula>AND(ISNUMBER(F18),ROUND(F18,2)=INT(ROUND(F18,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="263" priority="2">
-      <formula>AND(ISNUMBER(F18),ROUND(F18,2)&lt;&gt;INT(ROUND(F18,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="expression" dxfId="264" priority="1">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)=INT(ROUND(E19,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="265" priority="2">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)&lt;&gt;INT(ROUND(E19,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="expression" dxfId="266" priority="1">
-      <formula>AND(ISNUMBER(F19),ROUND(F19,2)=INT(ROUND(F19,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="267" priority="2">
-      <formula>AND(ISNUMBER(F19),ROUND(F19,2)&lt;&gt;INT(ROUND(F19,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="expression" dxfId="268" priority="1">
-      <formula>AND(ISNUMBER(F21),ROUND(F21,2)=INT(ROUND(F21,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="269" priority="2">
-      <formula>AND(ISNUMBER(F21),ROUND(F21,2)&lt;&gt;INT(ROUND(F21,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="15">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D13:D15">
       <formula1>0</formula1>
@@ -5953,174 +4100,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B18:E18"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="270" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="271" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="272" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="273" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="274" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="275" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="276" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="277" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="278" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="279" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="280" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="281" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="282" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="283" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="284" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="285" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="286" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="287" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="288" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="289" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="290" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="291" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="292" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="293" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="294" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="295" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="296" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="297" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="expression" dxfId="298" priority="1">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)=INT(ROUND(E14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="299" priority="2">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)&lt;&gt;INT(ROUND(E14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="300" priority="1">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)=INT(ROUND(F14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="301" priority="2">
-      <formula>AND(ISNUMBER(F14),ROUND(F14,2)&lt;&gt;INT(ROUND(F14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="expression" dxfId="302" priority="1">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)=INT(ROUND(E15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="303" priority="2">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)&lt;&gt;INT(ROUND(E15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="304" priority="1">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)=INT(ROUND(F15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="305" priority="2">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)&lt;&gt;INT(ROUND(F15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="expression" dxfId="306" priority="1">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)=INT(ROUND(E16,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="307" priority="2">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)&lt;&gt;INT(ROUND(E16,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="expression" dxfId="308" priority="1">
-      <formula>AND(ISNUMBER(F16),ROUND(F16,2)=INT(ROUND(F16,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="309" priority="2">
-      <formula>AND(ISNUMBER(F16),ROUND(F16,2)&lt;&gt;INT(ROUND(F16,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="expression" dxfId="310" priority="1">
-      <formula>AND(ISNUMBER(F18),ROUND(F18,2)=INT(ROUND(F18,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="311" priority="2">
-      <formula>AND(ISNUMBER(F18),ROUND(F18,2)&lt;&gt;INT(ROUND(F18,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D13:D16">
       <formula1>0</formula1>
@@ -6347,62 +4326,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="312" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="313" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="314" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="315" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="316" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="317" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="318" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="319" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="320" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="321" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="322" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="323" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="324" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="325" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
@@ -6614,62 +4537,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B9:E9"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="326" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="327" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="328" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="329" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="330" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="331" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="332" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="333" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="334" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="335" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="336" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="337" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="338" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="339" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
@@ -6869,62 +4736,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="340" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="341" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="342" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="343" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="344" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="345" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="346" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="347" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="348" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="349" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="350" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="351" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="352" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="353" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D6">
       <formula1>0</formula1>
@@ -7090,30 +4901,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="354" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="355" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="356" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="357" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="358" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="359" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -7799,30 +5586,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="360" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="361" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="362" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="363" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="364" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="365" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -7982,30 +5745,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="366" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="367" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="368" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="369" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="370" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="371" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -8188,46 +5927,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="372" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="373" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="374" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="375" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="376" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="377" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="378" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="379" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="380" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="381" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D5">
       <formula1>0</formula1>
@@ -8390,30 +6089,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="382" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="383" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="384" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="385" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="386" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="387" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -8573,30 +6248,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="388" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="389" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="390" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="391" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="392" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="393" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -8779,46 +6430,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="394" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="395" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="396" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="397" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="398" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="399" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="400" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="401" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="402" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="403" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D5">
       <formula1>0</formula1>
@@ -9315,206 +6926,6 @@
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="expression" dxfId="404" priority="1">
-      <formula>AND(ISNUMBER(E3),ROUND(E3,2)=INT(ROUND(E3,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="405" priority="2">
-      <formula>AND(ISNUMBER(E3),ROUND(E3,2)&lt;&gt;INT(ROUND(E3,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="406" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="407" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="408" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="409" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="410" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="411" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="412" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="413" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="414" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="415" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="416" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="417" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="418" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="419" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="420" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="421" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="expression" dxfId="422" priority="1">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)=INT(ROUND(E12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="423" priority="2">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)&lt;&gt;INT(ROUND(E12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="424" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="425" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="expression" dxfId="426" priority="1">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)=INT(ROUND(E14,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="427" priority="2">
-      <formula>AND(ISNUMBER(E14),ROUND(E14,2)&lt;&gt;INT(ROUND(E14,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="expression" dxfId="428" priority="1">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)=INT(ROUND(E15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="429" priority="2">
-      <formula>AND(ISNUMBER(E15),ROUND(E15,2)&lt;&gt;INT(ROUND(E15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="expression" dxfId="430" priority="1">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)=INT(ROUND(E16,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="431" priority="2">
-      <formula>AND(ISNUMBER(E16),ROUND(E16,2)&lt;&gt;INT(ROUND(E16,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="432" priority="1">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)=INT(ROUND(E17,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="433" priority="2">
-      <formula>AND(ISNUMBER(E17),ROUND(E17,2)&lt;&gt;INT(ROUND(E17,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="expression" dxfId="434" priority="1">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)=INT(ROUND(E18,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="435" priority="2">
-      <formula>AND(ISNUMBER(E18),ROUND(E18,2)&lt;&gt;INT(ROUND(E18,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="expression" dxfId="436" priority="1">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)=INT(ROUND(E19,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="437" priority="2">
-      <formula>AND(ISNUMBER(E19),ROUND(E19,2)&lt;&gt;INT(ROUND(E19,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
-    <cfRule type="expression" dxfId="438" priority="1">
-      <formula>AND(ISNUMBER(E20),ROUND(E20,2)=INT(ROUND(E20,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="439" priority="2">
-      <formula>AND(ISNUMBER(E20),ROUND(E20,2)&lt;&gt;INT(ROUND(E20,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="expression" dxfId="440" priority="1">
-      <formula>AND(ISNUMBER(E21),ROUND(E21,2)=INT(ROUND(E21,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="441" priority="2">
-      <formula>AND(ISNUMBER(E21),ROUND(E21,2)&lt;&gt;INT(ROUND(E21,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
-    <cfRule type="expression" dxfId="442" priority="1">
-      <formula>AND(ISNUMBER(E22),ROUND(E22,2)=INT(ROUND(E22,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="443" priority="2">
-      <formula>AND(ISNUMBER(E22),ROUND(E22,2)&lt;&gt;INT(ROUND(E22,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23">
-    <cfRule type="expression" dxfId="444" priority="1">
-      <formula>AND(ISNUMBER(E23),ROUND(E23,2)=INT(ROUND(E23,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="445" priority="2">
-      <formula>AND(ISNUMBER(E23),ROUND(E23,2)&lt;&gt;INT(ROUND(E23,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
-    <cfRule type="expression" dxfId="446" priority="1">
-      <formula>AND(ISNUMBER(E24),ROUND(E24,2)=INT(ROUND(E24,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="447" priority="2">
-      <formula>AND(ISNUMBER(E24),ROUND(E24,2)&lt;&gt;INT(ROUND(E24,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
-    <cfRule type="expression" dxfId="448" priority="1">
-      <formula>AND(ISNUMBER(E26),ROUND(E26,2)=INT(ROUND(E26,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="449" priority="2">
-      <formula>AND(ISNUMBER(E26),ROUND(E26,2)&lt;&gt;INT(ROUND(E26,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="expression" dxfId="450" priority="1">
-      <formula>AND(ISNUMBER(E27),ROUND(E27,2)=INT(ROUND(E27,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="451" priority="2">
-      <formula>AND(ISNUMBER(E27),ROUND(E27,2)&lt;&gt;INT(ROUND(E27,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E28">
-    <cfRule type="expression" dxfId="452" priority="1">
-      <formula>AND(ISNUMBER(E28),ROUND(E28,2)=INT(ROUND(E28,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="453" priority="2">
-      <formula>AND(ISNUMBER(E28),ROUND(E28,2)&lt;&gt;INT(ROUND(E28,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" firstPageNumber="29" useFirstPageNumber="1"/>
   <headerFooter>
@@ -10185,142 +7596,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B13:E13"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="10" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="14" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="16" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="20" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="22" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="24" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="26" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="28" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="30" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="32" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10:D11">
       <formula1>0</formula1>
@@ -10607,110 +7882,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B11:E11"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="34" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="36" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="38" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="40" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="42" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="44" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="46" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="48" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="50" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="52" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="54" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="56" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="58" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4:D9">
       <formula1>0</formula1>
@@ -11034,142 +8205,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B13:E13"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="60" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="62" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="64" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="66" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="68" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="70" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="72" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="74" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="76" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="78" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="80" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="82" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="84" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="86" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="88" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="90" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="92" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10:D11">
       <formula1>0</formula1>
@@ -11548,174 +8583,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B15:E15"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="94" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="96" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="98" priority="1">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)=INT(ROUND(E5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="2">
-      <formula>AND(ISNUMBER(E5),ROUND(E5,2)&lt;&gt;INT(ROUND(E5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="100" priority="1">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)=INT(ROUND(F5,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="2">
-      <formula>AND(ISNUMBER(F5),ROUND(F5,2)&lt;&gt;INT(ROUND(F5,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="102" priority="1">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)=INT(ROUND(E6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="2">
-      <formula>AND(ISNUMBER(E6),ROUND(E6,2)&lt;&gt;INT(ROUND(E6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="104" priority="1">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)=INT(ROUND(F6,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="2">
-      <formula>AND(ISNUMBER(F6),ROUND(F6,2)&lt;&gt;INT(ROUND(F6,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" dxfId="106" priority="1">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)=INT(ROUND(E7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="107" priority="2">
-      <formula>AND(ISNUMBER(E7),ROUND(E7,2)&lt;&gt;INT(ROUND(E7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="108" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="110" priority="1">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)=INT(ROUND(E8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="2">
-      <formula>AND(ISNUMBER(E8),ROUND(E8,2)&lt;&gt;INT(ROUND(E8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="expression" dxfId="112" priority="1">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)=INT(ROUND(F8,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="2">
-      <formula>AND(ISNUMBER(F8),ROUND(F8,2)&lt;&gt;INT(ROUND(F8,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="114" priority="1">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)=INT(ROUND(E9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="115" priority="2">
-      <formula>AND(ISNUMBER(E9),ROUND(E9,2)&lt;&gt;INT(ROUND(E9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="expression" dxfId="116" priority="1">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)=INT(ROUND(F9,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="117" priority="2">
-      <formula>AND(ISNUMBER(F9),ROUND(F9,2)&lt;&gt;INT(ROUND(F9,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="expression" dxfId="118" priority="1">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)=INT(ROUND(E10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="119" priority="2">
-      <formula>AND(ISNUMBER(E10),ROUND(E10,2)&lt;&gt;INT(ROUND(E10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="expression" dxfId="120" priority="1">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)=INT(ROUND(F10,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="2">
-      <formula>AND(ISNUMBER(F10),ROUND(F10,2)&lt;&gt;INT(ROUND(F10,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="expression" dxfId="122" priority="1">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)=INT(ROUND(E11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="2">
-      <formula>AND(ISNUMBER(E11),ROUND(E11,2)&lt;&gt;INT(ROUND(E11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="expression" dxfId="124" priority="1">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)=INT(ROUND(F11,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="125" priority="2">
-      <formula>AND(ISNUMBER(F11),ROUND(F11,2)&lt;&gt;INT(ROUND(F11,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="expression" dxfId="126" priority="1">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)=INT(ROUND(E12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="127" priority="2">
-      <formula>AND(ISNUMBER(E12),ROUND(E12,2)&lt;&gt;INT(ROUND(E12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="expression" dxfId="128" priority="1">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)=INT(ROUND(F12,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="2">
-      <formula>AND(ISNUMBER(F12),ROUND(F12,2)&lt;&gt;INT(ROUND(F12,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="130" priority="1">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)=INT(ROUND(E13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="2">
-      <formula>AND(ISNUMBER(E13),ROUND(E13,2)&lt;&gt;INT(ROUND(E13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="expression" dxfId="132" priority="1">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)=INT(ROUND(F13,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="2">
-      <formula>AND(ISNUMBER(F13),ROUND(F13,2)&lt;&gt;INT(ROUND(F13,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="134" priority="1">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)=INT(ROUND(F15,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="2">
-      <formula>AND(ISNUMBER(F15),ROUND(F15,2)&lt;&gt;INT(ROUND(F15,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D10:D13">
       <formula1>0</formula1>
@@ -11905,30 +8772,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="136" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="137" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="138" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="139" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="140" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
@@ -12088,30 +8931,6 @@
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="142" priority="1">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)=INT(ROUND(E4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="2">
-      <formula>AND(ISNUMBER(E4),ROUND(E4,2)&lt;&gt;INT(ROUND(E4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="expression" dxfId="144" priority="1">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)=INT(ROUND(F4,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="145" priority="2">
-      <formula>AND(ISNUMBER(F4),ROUND(F4,2)&lt;&gt;INT(ROUND(F4,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="146" priority="1">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)=INT(ROUND(F7,2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="147" priority="2">
-      <formula>AND(ISNUMBER(F7),ROUND(F7,2)&lt;&gt;INT(ROUND(F7,2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" error="יש להזין מספר לא שלילי" sqref="D4">
       <formula1>0</formula1>
